--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>18792200</v>
+        <v>19914400</v>
       </c>
       <c r="E8" s="3">
-        <v>14932900</v>
+        <v>18845900</v>
       </c>
       <c r="F8" s="3">
-        <v>11507500</v>
+        <v>14975500</v>
       </c>
       <c r="G8" s="3">
-        <v>13038400</v>
+        <v>11540400</v>
       </c>
       <c r="H8" s="3">
-        <v>12497000</v>
+        <v>13075700</v>
       </c>
       <c r="I8" s="3">
-        <v>12002300</v>
+        <v>12532700</v>
       </c>
       <c r="J8" s="3">
+        <v>12036600</v>
+      </c>
+      <c r="K8" s="3">
         <v>9909300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6460600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7019600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9823200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8852100</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>11974100</v>
+        <v>12602400</v>
       </c>
       <c r="E9" s="3">
-        <v>9351600</v>
+        <v>12008300</v>
       </c>
       <c r="F9" s="3">
-        <v>7356300</v>
+        <v>9378300</v>
       </c>
       <c r="G9" s="3">
-        <v>8027900</v>
+        <v>7377300</v>
       </c>
       <c r="H9" s="3">
-        <v>7609100</v>
+        <v>8050900</v>
       </c>
       <c r="I9" s="3">
-        <v>7320500</v>
+        <v>7630800</v>
       </c>
       <c r="J9" s="3">
+        <v>7341400</v>
+      </c>
+      <c r="K9" s="3">
         <v>6058600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12734500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14979800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6399700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5667900</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6818100</v>
+        <v>7312000</v>
       </c>
       <c r="E10" s="3">
-        <v>5581200</v>
+        <v>6837600</v>
       </c>
       <c r="F10" s="3">
-        <v>4151200</v>
+        <v>5597200</v>
       </c>
       <c r="G10" s="3">
-        <v>5010500</v>
+        <v>4163100</v>
       </c>
       <c r="H10" s="3">
-        <v>4887900</v>
+        <v>5024800</v>
       </c>
       <c r="I10" s="3">
-        <v>4681800</v>
+        <v>4901900</v>
       </c>
       <c r="J10" s="3">
+        <v>4695200</v>
+      </c>
+      <c r="K10" s="3">
         <v>3850700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-6273800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-7960200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3423500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3184200</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,87 +941,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>65100</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>62900</v>
+        <v>65300</v>
       </c>
       <c r="F14" s="3">
-        <v>98700</v>
+        <v>63100</v>
       </c>
       <c r="G14" s="3">
-        <v>27100</v>
+        <v>99000</v>
       </c>
       <c r="H14" s="3">
-        <v>51000</v>
+        <v>27200</v>
       </c>
       <c r="I14" s="3">
-        <v>27100</v>
-      </c>
-      <c r="J14" s="3" t="s">
+        <v>51100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>66400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>91500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>143500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>93300</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>100900</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="3">
-        <v>91100</v>
+        <v>101200</v>
       </c>
       <c r="F15" s="3">
-        <v>67300</v>
+        <v>91400</v>
       </c>
       <c r="G15" s="3">
-        <v>47700</v>
+        <v>67500</v>
       </c>
       <c r="H15" s="3">
-        <v>46700</v>
+        <v>47900</v>
       </c>
       <c r="I15" s="3">
-        <v>41200</v>
+        <v>46800</v>
       </c>
       <c r="J15" s="3">
+        <v>41300</v>
+      </c>
+      <c r="K15" s="3">
         <v>35800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>191900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>238200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>227300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>235000</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>16528900</v>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E17" s="3">
-        <v>13288000</v>
+        <v>16576100</v>
       </c>
       <c r="F17" s="3">
-        <v>10625400</v>
+        <v>13326000</v>
       </c>
       <c r="G17" s="3">
-        <v>11358900</v>
+        <v>10655800</v>
       </c>
       <c r="H17" s="3">
-        <v>11086500</v>
+        <v>11391300</v>
       </c>
       <c r="I17" s="3">
-        <v>10635200</v>
+        <v>11118200</v>
       </c>
       <c r="J17" s="3">
+        <v>10665600</v>
+      </c>
+      <c r="K17" s="3">
         <v>8986000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5685900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6176200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8729900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7833100</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>2263300</v>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>1644900</v>
+        <v>2269800</v>
       </c>
       <c r="F18" s="3">
-        <v>882100</v>
+        <v>1649600</v>
       </c>
       <c r="G18" s="3">
-        <v>1679600</v>
+        <v>884600</v>
       </c>
       <c r="H18" s="3">
-        <v>1410500</v>
+        <v>1684400</v>
       </c>
       <c r="I18" s="3">
-        <v>1367100</v>
+        <v>1414500</v>
       </c>
       <c r="J18" s="3">
+        <v>1371000</v>
+      </c>
+      <c r="K18" s="3">
         <v>923300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>774800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>843400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1093300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1018900</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>51000</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
-        <v>31500</v>
+        <v>51100</v>
       </c>
       <c r="F20" s="3">
-        <v>19500</v>
+        <v>31600</v>
       </c>
       <c r="G20" s="3">
-        <v>46700</v>
+        <v>19600</v>
       </c>
       <c r="H20" s="3">
-        <v>42300</v>
+        <v>46800</v>
       </c>
       <c r="I20" s="3">
-        <v>43400</v>
+        <v>42400</v>
       </c>
       <c r="J20" s="3">
+        <v>43500</v>
+      </c>
+      <c r="K20" s="3">
         <v>14100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>32700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-130400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3300</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>3199300</v>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>2524500</v>
+        <v>3214100</v>
       </c>
       <c r="F21" s="3">
-        <v>1690100</v>
+        <v>2537100</v>
       </c>
       <c r="G21" s="3">
-        <v>2419300</v>
+        <v>1700000</v>
       </c>
       <c r="H21" s="3">
-        <v>2008100</v>
+        <v>2430600</v>
       </c>
       <c r="I21" s="3">
-        <v>1942000</v>
+        <v>2017400</v>
       </c>
       <c r="J21" s="3">
+        <v>1950900</v>
+      </c>
+      <c r="K21" s="3">
         <v>1340900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1034300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1139900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1329900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1390600</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>191000</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>176900</v>
+        <v>191500</v>
       </c>
       <c r="F22" s="3">
-        <v>147600</v>
+        <v>177400</v>
       </c>
       <c r="G22" s="3">
-        <v>148600</v>
+        <v>148000</v>
       </c>
       <c r="H22" s="3">
-        <v>145400</v>
+        <v>149100</v>
       </c>
       <c r="I22" s="3">
-        <v>153000</v>
+        <v>145800</v>
       </c>
       <c r="J22" s="3">
+        <v>153400</v>
+      </c>
+      <c r="K22" s="3">
         <v>157300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>129600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>133200</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>103200</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2123300</v>
+        <v>2397100</v>
       </c>
       <c r="E23" s="3">
-        <v>1499500</v>
+        <v>2129400</v>
       </c>
       <c r="F23" s="3">
-        <v>754100</v>
+        <v>1503800</v>
       </c>
       <c r="G23" s="3">
-        <v>1577600</v>
+        <v>756200</v>
       </c>
       <c r="H23" s="3">
-        <v>1307400</v>
+        <v>1582100</v>
       </c>
       <c r="I23" s="3">
-        <v>1257500</v>
+        <v>1311200</v>
       </c>
       <c r="J23" s="3">
+        <v>1261100</v>
+      </c>
+      <c r="K23" s="3">
         <v>780100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>657400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>742900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>962900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>919000</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>473100</v>
+        <v>581000</v>
       </c>
       <c r="E24" s="3">
-        <v>427500</v>
+        <v>474400</v>
       </c>
       <c r="F24" s="3">
-        <v>213700</v>
+        <v>428700</v>
       </c>
       <c r="G24" s="3">
-        <v>394900</v>
+        <v>214400</v>
       </c>
       <c r="H24" s="3">
-        <v>350500</v>
+        <v>396100</v>
       </c>
       <c r="I24" s="3">
-        <v>163800</v>
+        <v>351500</v>
       </c>
       <c r="J24" s="3">
+        <v>164300</v>
+      </c>
+      <c r="K24" s="3">
         <v>184500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>133700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>196500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>165100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>175700</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>1650300</v>
+      <c r="D26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E26" s="3">
-        <v>1072000</v>
+        <v>1655000</v>
       </c>
       <c r="F26" s="3">
-        <v>540300</v>
+        <v>1075000</v>
       </c>
       <c r="G26" s="3">
-        <v>1182700</v>
+        <v>541900</v>
       </c>
       <c r="H26" s="3">
-        <v>957000</v>
+        <v>1186000</v>
       </c>
       <c r="I26" s="3">
-        <v>1093700</v>
+        <v>959700</v>
       </c>
       <c r="J26" s="3">
+        <v>1096800</v>
+      </c>
+      <c r="K26" s="3">
         <v>595700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>523700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>546500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>797900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>743300</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1636200</v>
+      <c r="D27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E27" s="3">
-        <v>1065500</v>
+        <v>1640900</v>
       </c>
       <c r="F27" s="3">
-        <v>540300</v>
+        <v>1068500</v>
       </c>
       <c r="G27" s="3">
-        <v>1182700</v>
+        <v>541900</v>
       </c>
       <c r="H27" s="3">
-        <v>957000</v>
+        <v>1186000</v>
       </c>
       <c r="I27" s="3">
-        <v>1093700</v>
+        <v>959700</v>
       </c>
       <c r="J27" s="3">
+        <v>1096800</v>
+      </c>
+      <c r="K27" s="3">
         <v>595700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>523700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>546500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>797900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>743300</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1481,14 +1541,14 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>29300</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>-347200</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>29400</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-348200</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-51000</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>-31500</v>
+        <v>-51100</v>
       </c>
       <c r="F32" s="3">
-        <v>-19500</v>
+        <v>-31600</v>
       </c>
       <c r="G32" s="3">
-        <v>-46700</v>
+        <v>-19600</v>
       </c>
       <c r="H32" s="3">
-        <v>-42300</v>
+        <v>-46800</v>
       </c>
       <c r="I32" s="3">
-        <v>-43400</v>
+        <v>-42400</v>
       </c>
       <c r="J32" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-32700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>130400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3300</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>1636200</v>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E33" s="3">
-        <v>1065500</v>
+        <v>1640900</v>
       </c>
       <c r="F33" s="3">
-        <v>540300</v>
+        <v>1068500</v>
       </c>
       <c r="G33" s="3">
-        <v>1182700</v>
+        <v>541900</v>
       </c>
       <c r="H33" s="3">
-        <v>986300</v>
+        <v>1186000</v>
       </c>
       <c r="I33" s="3">
-        <v>746500</v>
+        <v>989100</v>
       </c>
       <c r="J33" s="3">
+        <v>748600</v>
+      </c>
+      <c r="K33" s="3">
         <v>595700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>523700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>546500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>797900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>743300</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>1636200</v>
+      <c r="D35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E35" s="3">
-        <v>1065500</v>
+        <v>1640900</v>
       </c>
       <c r="F35" s="3">
-        <v>540300</v>
+        <v>1068500</v>
       </c>
       <c r="G35" s="3">
-        <v>1182700</v>
+        <v>541900</v>
       </c>
       <c r="H35" s="3">
-        <v>986300</v>
+        <v>1186000</v>
       </c>
       <c r="I35" s="3">
-        <v>746500</v>
+        <v>989100</v>
       </c>
       <c r="J35" s="3">
+        <v>748600</v>
+      </c>
+      <c r="K35" s="3">
         <v>595700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>523700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>546500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>797900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>743300</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,242 +1900,261 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>532700</v>
+        <v>1544000</v>
       </c>
       <c r="E41" s="3">
-        <v>768200</v>
+        <v>534300</v>
       </c>
       <c r="F41" s="3">
-        <v>697700</v>
+        <v>770400</v>
       </c>
       <c r="G41" s="3">
-        <v>184400</v>
+        <v>699600</v>
       </c>
       <c r="H41" s="3">
+        <v>185000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>303600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>330800</v>
+      </c>
+      <c r="K41" s="3">
         <v>302700</v>
       </c>
-      <c r="I41" s="3">
-        <v>329800</v>
-      </c>
-      <c r="J41" s="3">
-        <v>302700</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>412400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>631200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>410300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>791700</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1249900</v>
+        <v>618000</v>
       </c>
       <c r="E42" s="3">
-        <v>821300</v>
+        <v>1253500</v>
       </c>
       <c r="F42" s="3">
-        <v>954800</v>
+        <v>823700</v>
       </c>
       <c r="G42" s="3">
-        <v>158400</v>
+        <v>957500</v>
       </c>
       <c r="H42" s="3">
-        <v>32500</v>
+        <v>158900</v>
       </c>
       <c r="I42" s="3">
-        <v>60800</v>
+        <v>32600</v>
       </c>
       <c r="J42" s="3">
+        <v>60900</v>
+      </c>
+      <c r="K42" s="3">
         <v>116100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>79600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36100</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2918700</v>
+        <v>2968300</v>
       </c>
       <c r="E43" s="3">
-        <v>2706000</v>
+        <v>2927000</v>
       </c>
       <c r="F43" s="3">
-        <v>1744700</v>
+        <v>2713700</v>
       </c>
       <c r="G43" s="3">
-        <v>2136400</v>
+        <v>1749700</v>
       </c>
       <c r="H43" s="3">
-        <v>2076700</v>
+        <v>2142500</v>
       </c>
       <c r="I43" s="3">
-        <v>2418500</v>
+        <v>2082600</v>
       </c>
       <c r="J43" s="3">
+        <v>2425400</v>
+      </c>
+      <c r="K43" s="3">
         <v>2462900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3935200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4700400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1918700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1644800</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1497300</v>
+        <v>1475500</v>
       </c>
       <c r="E44" s="3">
-        <v>1255300</v>
+        <v>1501600</v>
       </c>
       <c r="F44" s="3">
-        <v>738900</v>
+        <v>1258900</v>
       </c>
       <c r="G44" s="3">
-        <v>784500</v>
+        <v>741000</v>
       </c>
       <c r="H44" s="3">
-        <v>751900</v>
+        <v>786700</v>
       </c>
       <c r="I44" s="3">
-        <v>705300</v>
+        <v>754100</v>
       </c>
       <c r="J44" s="3">
+        <v>707300</v>
+      </c>
+      <c r="K44" s="3">
         <v>730200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1100400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1282700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>540700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>423800</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>900500</v>
+        <v>581000</v>
       </c>
       <c r="E45" s="3">
-        <v>698700</v>
+        <v>903100</v>
       </c>
       <c r="F45" s="3">
-        <v>286400</v>
+        <v>700700</v>
       </c>
       <c r="G45" s="3">
-        <v>103100</v>
+        <v>287300</v>
       </c>
       <c r="H45" s="3">
-        <v>81400</v>
+        <v>103400</v>
       </c>
       <c r="I45" s="3">
-        <v>81400</v>
+        <v>81600</v>
       </c>
       <c r="J45" s="3">
+        <v>81600</v>
+      </c>
+      <c r="K45" s="3">
         <v>104200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>314400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>513700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>202200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>172400</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7099200</v>
+        <v>7186900</v>
       </c>
       <c r="E46" s="3">
-        <v>6249600</v>
+        <v>7119400</v>
       </c>
       <c r="F46" s="3">
-        <v>4422500</v>
+        <v>6267500</v>
       </c>
       <c r="G46" s="3">
-        <v>3366800</v>
+        <v>4435100</v>
       </c>
       <c r="H46" s="3">
-        <v>3245200</v>
+        <v>3376400</v>
       </c>
       <c r="I46" s="3">
-        <v>3595700</v>
+        <v>3254500</v>
       </c>
       <c r="J46" s="3">
+        <v>3606000</v>
+      </c>
+      <c r="K46" s="3">
         <v>3716100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1922200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2267200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3071800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3032700</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2087,87 +2191,96 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5643100</v>
+        <v>5814800</v>
       </c>
       <c r="E48" s="3">
-        <v>5694100</v>
+        <v>5659200</v>
       </c>
       <c r="F48" s="3">
-        <v>4188100</v>
+        <v>5710300</v>
       </c>
       <c r="G48" s="3">
-        <v>4562400</v>
+        <v>4200100</v>
       </c>
       <c r="H48" s="3">
-        <v>4218500</v>
+        <v>4575500</v>
       </c>
       <c r="I48" s="3">
-        <v>4163100</v>
+        <v>4230500</v>
       </c>
       <c r="J48" s="3">
+        <v>4175000</v>
+      </c>
+      <c r="K48" s="3">
         <v>4332400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5414300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6150200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2814700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2549600</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18558900</v>
+        <v>18398700</v>
       </c>
       <c r="E49" s="3">
-        <v>18729300</v>
+        <v>18612000</v>
       </c>
       <c r="F49" s="3">
-        <v>11860100</v>
+        <v>18782800</v>
       </c>
       <c r="G49" s="3">
-        <v>11963200</v>
+        <v>11894000</v>
       </c>
       <c r="H49" s="3">
-        <v>11828700</v>
+        <v>11997400</v>
       </c>
       <c r="I49" s="3">
-        <v>11830800</v>
+        <v>11862500</v>
       </c>
       <c r="J49" s="3">
+        <v>11864600</v>
+      </c>
+      <c r="K49" s="3">
         <v>11686500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10163100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11288700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4937900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4452400</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>503400</v>
+        <v>430900</v>
       </c>
       <c r="E52" s="3">
-        <v>889700</v>
+        <v>504900</v>
       </c>
       <c r="F52" s="3">
-        <v>401400</v>
+        <v>892200</v>
       </c>
       <c r="G52" s="3">
-        <v>380800</v>
+        <v>402600</v>
       </c>
       <c r="H52" s="3">
-        <v>472000</v>
+        <v>381900</v>
       </c>
       <c r="I52" s="3">
-        <v>150800</v>
+        <v>473300</v>
       </c>
       <c r="J52" s="3">
+        <v>151200</v>
+      </c>
+      <c r="K52" s="3">
         <v>411200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>372600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>493400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>569400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>407400</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31804600</v>
+        <v>31831300</v>
       </c>
       <c r="E54" s="3">
-        <v>31562600</v>
+        <v>31895500</v>
       </c>
       <c r="F54" s="3">
-        <v>20872100</v>
+        <v>31652800</v>
       </c>
       <c r="G54" s="3">
-        <v>20273200</v>
+        <v>20931800</v>
       </c>
       <c r="H54" s="3">
-        <v>19764400</v>
+        <v>20331100</v>
       </c>
       <c r="I54" s="3">
-        <v>19740500</v>
+        <v>19820800</v>
       </c>
       <c r="J54" s="3">
+        <v>19796900</v>
+      </c>
+      <c r="K54" s="3">
         <v>20146300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7141500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7957900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11393800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10442000</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2377200</v>
+        <v>5695100</v>
       </c>
       <c r="E57" s="3">
-        <v>1834700</v>
+        <v>2384000</v>
       </c>
       <c r="F57" s="3">
-        <v>1219500</v>
+        <v>1840000</v>
       </c>
       <c r="G57" s="3">
-        <v>1234700</v>
+        <v>1223000</v>
       </c>
       <c r="H57" s="3">
-        <v>1198900</v>
+        <v>1238300</v>
       </c>
       <c r="I57" s="3">
-        <v>1146800</v>
+        <v>1202400</v>
       </c>
       <c r="J57" s="3">
+        <v>1150100</v>
+      </c>
+      <c r="K57" s="3">
         <v>980800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2469300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2853200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>754800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1481200</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1449600</v>
+        <v>1414500</v>
       </c>
       <c r="E58" s="3">
-        <v>1464800</v>
+        <v>1453700</v>
       </c>
       <c r="F58" s="3">
-        <v>873400</v>
+        <v>1468900</v>
       </c>
       <c r="G58" s="3">
-        <v>866900</v>
+        <v>875900</v>
       </c>
       <c r="H58" s="3">
-        <v>532700</v>
+        <v>869400</v>
       </c>
       <c r="I58" s="3">
-        <v>297300</v>
+        <v>534300</v>
       </c>
       <c r="J58" s="3">
+        <v>298100</v>
+      </c>
+      <c r="K58" s="3">
         <v>949400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>890100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1304100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>132800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>693900</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4107800</v>
+        <v>809500</v>
       </c>
       <c r="E59" s="3">
-        <v>3311400</v>
+        <v>4119500</v>
       </c>
       <c r="F59" s="3">
-        <v>2398900</v>
+        <v>3320900</v>
       </c>
       <c r="G59" s="3">
-        <v>2363100</v>
+        <v>2405800</v>
       </c>
       <c r="H59" s="3">
-        <v>2382700</v>
+        <v>2369900</v>
       </c>
       <c r="I59" s="3">
-        <v>2122300</v>
+        <v>2389500</v>
       </c>
       <c r="J59" s="3">
+        <v>2128300</v>
+      </c>
+      <c r="K59" s="3">
         <v>2140700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2534600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2900700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1738100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>656600</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7934600</v>
+        <v>7919200</v>
       </c>
       <c r="E60" s="3">
-        <v>6610900</v>
+        <v>7957300</v>
       </c>
       <c r="F60" s="3">
-        <v>4491900</v>
+        <v>6629800</v>
       </c>
       <c r="G60" s="3">
-        <v>4464800</v>
+        <v>4504700</v>
       </c>
       <c r="H60" s="3">
-        <v>4114300</v>
+        <v>4477500</v>
       </c>
       <c r="I60" s="3">
-        <v>3566400</v>
+        <v>4126100</v>
       </c>
       <c r="J60" s="3">
+        <v>3576600</v>
+      </c>
+      <c r="K60" s="3">
         <v>4070900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2047700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2433200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2625700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2831700</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11469500</v>
+        <v>10985500</v>
       </c>
       <c r="E61" s="3">
-        <v>12792100</v>
+        <v>11502300</v>
       </c>
       <c r="F61" s="3">
-        <v>6924500</v>
+        <v>12828700</v>
       </c>
       <c r="G61" s="3">
-        <v>6099900</v>
+        <v>6944300</v>
       </c>
       <c r="H61" s="3">
-        <v>5562800</v>
+        <v>6117300</v>
       </c>
       <c r="I61" s="3">
-        <v>5939300</v>
+        <v>5578700</v>
       </c>
       <c r="J61" s="3">
+        <v>5956300</v>
+      </c>
+      <c r="K61" s="3">
         <v>6034800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3186900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3083600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4457000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3111700</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4320500</v>
+        <v>4247900</v>
       </c>
       <c r="E62" s="3">
-        <v>4336700</v>
+        <v>4332800</v>
       </c>
       <c r="F62" s="3">
-        <v>2918700</v>
+        <v>4349100</v>
       </c>
       <c r="G62" s="3">
-        <v>3029300</v>
+        <v>2927000</v>
       </c>
       <c r="H62" s="3">
-        <v>2965300</v>
+        <v>3038000</v>
       </c>
       <c r="I62" s="3">
-        <v>2981600</v>
+        <v>2973800</v>
       </c>
       <c r="J62" s="3">
+        <v>2990100</v>
+      </c>
+      <c r="K62" s="3">
         <v>3030400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2151800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2453500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1583800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1541600</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23724600</v>
+        <v>23152600</v>
       </c>
       <c r="E66" s="3">
-        <v>23931800</v>
+        <v>23792400</v>
       </c>
       <c r="F66" s="3">
-        <v>14335000</v>
+        <v>24000200</v>
       </c>
       <c r="G66" s="3">
-        <v>13594000</v>
+        <v>14376000</v>
       </c>
       <c r="H66" s="3">
-        <v>12642400</v>
+        <v>13632800</v>
       </c>
       <c r="I66" s="3">
-        <v>12487300</v>
+        <v>12678500</v>
       </c>
       <c r="J66" s="3">
+        <v>12522900</v>
+      </c>
+      <c r="K66" s="3">
         <v>13136100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6252400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6617700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8666500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7485100</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8284000</v>
+        <v>8372900</v>
       </c>
       <c r="E72" s="3">
-        <v>7561400</v>
+        <v>8307600</v>
       </c>
       <c r="F72" s="3">
-        <v>6906000</v>
+        <v>7583000</v>
       </c>
       <c r="G72" s="3">
-        <v>6967900</v>
+        <v>6925800</v>
       </c>
       <c r="H72" s="3">
-        <v>7550500</v>
+        <v>6987800</v>
       </c>
       <c r="I72" s="3">
-        <v>7655800</v>
+        <v>7572100</v>
       </c>
       <c r="J72" s="3">
+        <v>7677600</v>
+      </c>
+      <c r="K72" s="3">
         <v>7335700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4037300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3770100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1886400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1236300</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8080000</v>
+        <v>8678700</v>
       </c>
       <c r="E76" s="3">
-        <v>7630800</v>
+        <v>8103100</v>
       </c>
       <c r="F76" s="3">
-        <v>6537100</v>
+        <v>7652600</v>
       </c>
       <c r="G76" s="3">
-        <v>6679300</v>
+        <v>6555800</v>
       </c>
       <c r="H76" s="3">
-        <v>7121900</v>
+        <v>6698300</v>
       </c>
       <c r="I76" s="3">
-        <v>7253200</v>
+        <v>7142300</v>
       </c>
       <c r="J76" s="3">
+        <v>7273900</v>
+      </c>
+      <c r="K76" s="3">
         <v>7010200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>889100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1340200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2727300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2956900</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>1636200</v>
+      <c r="D81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E81" s="3">
-        <v>1065500</v>
+        <v>1640900</v>
       </c>
       <c r="F81" s="3">
-        <v>540300</v>
+        <v>1068500</v>
       </c>
       <c r="G81" s="3">
-        <v>1182700</v>
+        <v>541900</v>
       </c>
       <c r="H81" s="3">
-        <v>986300</v>
+        <v>1186000</v>
       </c>
       <c r="I81" s="3">
-        <v>746500</v>
+        <v>989100</v>
       </c>
       <c r="J81" s="3">
+        <v>748600</v>
+      </c>
+      <c r="K81" s="3">
         <v>595700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>523700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>546500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>797900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>743300</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>885400</v>
+        <v>861800</v>
       </c>
       <c r="E83" s="3">
-        <v>848500</v>
+        <v>887900</v>
       </c>
       <c r="F83" s="3">
-        <v>788800</v>
+        <v>850900</v>
       </c>
       <c r="G83" s="3">
-        <v>693300</v>
+        <v>791000</v>
       </c>
       <c r="H83" s="3">
-        <v>555500</v>
+        <v>695300</v>
       </c>
       <c r="I83" s="3">
-        <v>531700</v>
+        <v>557100</v>
       </c>
       <c r="J83" s="3">
+        <v>533200</v>
+      </c>
+      <c r="K83" s="3">
         <v>403600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>252100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>263100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>368400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>367800</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3181200</v>
+        <v>3053200</v>
       </c>
       <c r="E89" s="3">
-        <v>2296900</v>
+        <v>3190300</v>
       </c>
       <c r="F89" s="3">
-        <v>1616700</v>
+        <v>2303500</v>
       </c>
       <c r="G89" s="3">
-        <v>2065800</v>
+        <v>1621300</v>
       </c>
       <c r="H89" s="3">
-        <v>1959500</v>
+        <v>2071700</v>
       </c>
       <c r="I89" s="3">
-        <v>1761000</v>
+        <v>1965100</v>
       </c>
       <c r="J89" s="3">
+        <v>1766000</v>
+      </c>
+      <c r="K89" s="3">
         <v>1349700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>941200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>920200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>996400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1039800</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-542500</v>
+        <v>-731200</v>
       </c>
       <c r="E91" s="3">
+        <v>-544100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-379700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-378700</v>
       </c>
-      <c r="F91" s="3">
-        <v>-377600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-549000</v>
-      </c>
       <c r="H91" s="3">
-        <v>-569600</v>
+        <v>-550600</v>
       </c>
       <c r="I91" s="3">
-        <v>-525100</v>
+        <v>-571300</v>
       </c>
       <c r="J91" s="3">
+        <v>-526600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-498000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-625800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-625500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-374400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-415000</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-699800</v>
+        <v>-1019500</v>
       </c>
       <c r="E94" s="3">
-        <v>-6081400</v>
+        <v>-701800</v>
       </c>
       <c r="F94" s="3">
-        <v>-401500</v>
+        <v>-6098800</v>
       </c>
       <c r="G94" s="3">
-        <v>-649900</v>
+        <v>-402600</v>
       </c>
       <c r="H94" s="3">
-        <v>-646700</v>
+        <v>-651800</v>
       </c>
       <c r="I94" s="3">
-        <v>-529500</v>
+        <v>-648500</v>
       </c>
       <c r="J94" s="3">
+        <v>-531000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-415600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-277700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-233700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-394700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-409600</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-827900</v>
+        <v>-915100</v>
       </c>
       <c r="E96" s="3">
-        <v>-692200</v>
+        <v>-830200</v>
       </c>
       <c r="F96" s="3">
-        <v>-418800</v>
+        <v>-694200</v>
       </c>
       <c r="G96" s="3">
-        <v>-622800</v>
+        <v>-420000</v>
       </c>
       <c r="H96" s="3">
-        <v>-556600</v>
+        <v>-624600</v>
       </c>
       <c r="I96" s="3">
-        <v>-530600</v>
+        <v>-558200</v>
       </c>
       <c r="J96" s="3">
+        <v>-532100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-221300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-499200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-486600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-254800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-205300</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2469500</v>
+        <v>-1982500</v>
       </c>
       <c r="E100" s="3">
-        <v>3568600</v>
+        <v>-2476500</v>
       </c>
       <c r="F100" s="3">
-        <v>108500</v>
+        <v>3578800</v>
       </c>
       <c r="G100" s="3">
-        <v>-1412700</v>
+        <v>108800</v>
       </c>
       <c r="H100" s="3">
-        <v>-1366000</v>
+        <v>-1416700</v>
       </c>
       <c r="I100" s="3">
-        <v>-1249900</v>
+        <v>-1369900</v>
       </c>
       <c r="J100" s="3">
+        <v>-1253500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-679200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-699200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-764400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1071800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-610500</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-33600</v>
+        <v>-16300</v>
       </c>
       <c r="E101" s="3">
-        <v>90100</v>
+        <v>-33700</v>
       </c>
       <c r="F101" s="3">
+        <v>90300</v>
+      </c>
+      <c r="G101" s="3">
         <v>-14100</v>
       </c>
-      <c r="G101" s="3">
-        <v>4300</v>
-      </c>
       <c r="H101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>17900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>20900</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-21700</v>
+        <v>-51100</v>
       </c>
       <c r="E102" s="3">
-        <v>-125900</v>
+        <v>-21800</v>
       </c>
       <c r="F102" s="3">
-        <v>1309600</v>
+        <v>-126200</v>
       </c>
       <c r="G102" s="3">
+        <v>1313300</v>
+      </c>
+      <c r="H102" s="3">
         <v>7600</v>
       </c>
-      <c r="H102" s="3">
-        <v>-55300</v>
-      </c>
       <c r="I102" s="3">
-        <v>-28200</v>
+        <v>-55500</v>
       </c>
       <c r="J102" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="K102" s="3">
         <v>249600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-452200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>40600</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19914400</v>
+        <v>19779000</v>
       </c>
       <c r="E8" s="3">
-        <v>18845900</v>
+        <v>18717700</v>
       </c>
       <c r="F8" s="3">
-        <v>14975500</v>
+        <v>14873700</v>
       </c>
       <c r="G8" s="3">
-        <v>11540400</v>
+        <v>11461900</v>
       </c>
       <c r="H8" s="3">
-        <v>13075700</v>
+        <v>12986800</v>
       </c>
       <c r="I8" s="3">
-        <v>12532700</v>
+        <v>12447500</v>
       </c>
       <c r="J8" s="3">
-        <v>12036600</v>
+        <v>11954700</v>
       </c>
       <c r="K8" s="3">
         <v>9909300</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12602400</v>
+        <v>12423700</v>
       </c>
       <c r="E9" s="3">
-        <v>12008300</v>
+        <v>11926600</v>
       </c>
       <c r="F9" s="3">
-        <v>9378300</v>
+        <v>9314600</v>
       </c>
       <c r="G9" s="3">
-        <v>7377300</v>
+        <v>7327100</v>
       </c>
       <c r="H9" s="3">
-        <v>8050900</v>
+        <v>7996100</v>
       </c>
       <c r="I9" s="3">
-        <v>7630800</v>
+        <v>7578900</v>
       </c>
       <c r="J9" s="3">
-        <v>7341400</v>
+        <v>7291500</v>
       </c>
       <c r="K9" s="3">
         <v>6058600</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7312000</v>
+        <v>7355200</v>
       </c>
       <c r="E10" s="3">
-        <v>6837600</v>
+        <v>6791100</v>
       </c>
       <c r="F10" s="3">
-        <v>5597200</v>
+        <v>5559100</v>
       </c>
       <c r="G10" s="3">
-        <v>4163100</v>
+        <v>4134800</v>
       </c>
       <c r="H10" s="3">
-        <v>5024800</v>
+        <v>4990700</v>
       </c>
       <c r="I10" s="3">
-        <v>4901900</v>
+        <v>4868600</v>
       </c>
       <c r="J10" s="3">
-        <v>4695200</v>
+        <v>4663200</v>
       </c>
       <c r="K10" s="3">
         <v>3850700</v>
@@ -950,26 +950,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>35700</v>
       </c>
       <c r="E14" s="3">
-        <v>65300</v>
+        <v>64800</v>
       </c>
       <c r="F14" s="3">
-        <v>63100</v>
+        <v>62700</v>
       </c>
       <c r="G14" s="3">
-        <v>99000</v>
+        <v>98300</v>
       </c>
       <c r="H14" s="3">
-        <v>27200</v>
+        <v>27000</v>
       </c>
       <c r="I14" s="3">
-        <v>51100</v>
+        <v>50800</v>
       </c>
       <c r="J14" s="3">
-        <v>27200</v>
+        <v>27000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -992,26 +992,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>112400</v>
       </c>
       <c r="E15" s="3">
-        <v>101200</v>
+        <v>100500</v>
       </c>
       <c r="F15" s="3">
-        <v>91400</v>
+        <v>90800</v>
       </c>
       <c r="G15" s="3">
-        <v>67500</v>
+        <v>67000</v>
       </c>
       <c r="H15" s="3">
-        <v>47900</v>
+        <v>47600</v>
       </c>
       <c r="I15" s="3">
-        <v>46800</v>
+        <v>46500</v>
       </c>
       <c r="J15" s="3">
-        <v>41300</v>
+        <v>41100</v>
       </c>
       <c r="K15" s="3">
         <v>35800</v>
@@ -1049,26 +1049,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>17251200</v>
       </c>
       <c r="E17" s="3">
-        <v>16576100</v>
+        <v>16463400</v>
       </c>
       <c r="F17" s="3">
-        <v>13326000</v>
+        <v>13235300</v>
       </c>
       <c r="G17" s="3">
-        <v>10655800</v>
+        <v>10583300</v>
       </c>
       <c r="H17" s="3">
-        <v>11391300</v>
+        <v>11313800</v>
       </c>
       <c r="I17" s="3">
-        <v>11118200</v>
+        <v>11042600</v>
       </c>
       <c r="J17" s="3">
-        <v>10665600</v>
+        <v>10593000</v>
       </c>
       <c r="K17" s="3">
         <v>8986000</v>
@@ -1091,26 +1091,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>2527800</v>
       </c>
       <c r="E18" s="3">
-        <v>2269800</v>
+        <v>2254300</v>
       </c>
       <c r="F18" s="3">
-        <v>1649600</v>
+        <v>1638300</v>
       </c>
       <c r="G18" s="3">
-        <v>884600</v>
+        <v>878600</v>
       </c>
       <c r="H18" s="3">
-        <v>1684400</v>
+        <v>1672900</v>
       </c>
       <c r="I18" s="3">
-        <v>1414500</v>
+        <v>1404900</v>
       </c>
       <c r="J18" s="3">
-        <v>1371000</v>
+        <v>1361700</v>
       </c>
       <c r="K18" s="3">
         <v>923300</v>
@@ -1151,26 +1151,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>46500</v>
       </c>
       <c r="E20" s="3">
-        <v>51100</v>
+        <v>50800</v>
       </c>
       <c r="F20" s="3">
-        <v>31600</v>
+        <v>31300</v>
       </c>
       <c r="G20" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="H20" s="3">
-        <v>46800</v>
+        <v>46500</v>
       </c>
       <c r="I20" s="3">
-        <v>42400</v>
+        <v>42100</v>
       </c>
       <c r="J20" s="3">
-        <v>43500</v>
+        <v>43200</v>
       </c>
       <c r="K20" s="3">
         <v>14100</v>
@@ -1193,26 +1193,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>3424700</v>
       </c>
       <c r="E21" s="3">
-        <v>3214100</v>
+        <v>3181400</v>
       </c>
       <c r="F21" s="3">
-        <v>2537100</v>
+        <v>2509500</v>
       </c>
       <c r="G21" s="3">
-        <v>1700000</v>
+        <v>1678800</v>
       </c>
       <c r="H21" s="3">
-        <v>2430600</v>
+        <v>2405600</v>
       </c>
       <c r="I21" s="3">
-        <v>2017400</v>
+        <v>1996900</v>
       </c>
       <c r="J21" s="3">
-        <v>1950900</v>
+        <v>1931100</v>
       </c>
       <c r="K21" s="3">
         <v>1340900</v>
@@ -1235,26 +1235,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>193400</v>
       </c>
       <c r="E22" s="3">
-        <v>191500</v>
+        <v>190200</v>
       </c>
       <c r="F22" s="3">
-        <v>177400</v>
+        <v>176200</v>
       </c>
       <c r="G22" s="3">
-        <v>148000</v>
+        <v>147000</v>
       </c>
       <c r="H22" s="3">
-        <v>149100</v>
+        <v>148100</v>
       </c>
       <c r="I22" s="3">
-        <v>145800</v>
+        <v>144800</v>
       </c>
       <c r="J22" s="3">
-        <v>153400</v>
+        <v>152400</v>
       </c>
       <c r="K22" s="3">
         <v>157300</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2397100</v>
+        <v>2380800</v>
       </c>
       <c r="E23" s="3">
-        <v>2129400</v>
+        <v>2114900</v>
       </c>
       <c r="F23" s="3">
-        <v>1503800</v>
+        <v>1493500</v>
       </c>
       <c r="G23" s="3">
-        <v>756200</v>
+        <v>751100</v>
       </c>
       <c r="H23" s="3">
-        <v>1582100</v>
+        <v>1571300</v>
       </c>
       <c r="I23" s="3">
-        <v>1311200</v>
+        <v>1302200</v>
       </c>
       <c r="J23" s="3">
-        <v>1261100</v>
+        <v>1252500</v>
       </c>
       <c r="K23" s="3">
         <v>780100</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>581000</v>
+        <v>577100</v>
       </c>
       <c r="E24" s="3">
-        <v>474400</v>
+        <v>471200</v>
       </c>
       <c r="F24" s="3">
-        <v>428700</v>
+        <v>425800</v>
       </c>
       <c r="G24" s="3">
-        <v>214400</v>
+        <v>212900</v>
       </c>
       <c r="H24" s="3">
-        <v>396100</v>
+        <v>393400</v>
       </c>
       <c r="I24" s="3">
-        <v>351500</v>
+        <v>349100</v>
       </c>
       <c r="J24" s="3">
-        <v>164300</v>
+        <v>163200</v>
       </c>
       <c r="K24" s="3">
         <v>184500</v>
@@ -1403,26 +1403,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>1803700</v>
       </c>
       <c r="E26" s="3">
-        <v>1655000</v>
+        <v>1643700</v>
       </c>
       <c r="F26" s="3">
-        <v>1075000</v>
+        <v>1067700</v>
       </c>
       <c r="G26" s="3">
-        <v>541900</v>
+        <v>538200</v>
       </c>
       <c r="H26" s="3">
-        <v>1186000</v>
+        <v>1178000</v>
       </c>
       <c r="I26" s="3">
-        <v>959700</v>
+        <v>953200</v>
       </c>
       <c r="J26" s="3">
-        <v>1096800</v>
+        <v>1089300</v>
       </c>
       <c r="K26" s="3">
         <v>595700</v>
@@ -1445,26 +1445,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>1803700</v>
       </c>
       <c r="E27" s="3">
-        <v>1640900</v>
+        <v>1629700</v>
       </c>
       <c r="F27" s="3">
-        <v>1068500</v>
+        <v>1061200</v>
       </c>
       <c r="G27" s="3">
-        <v>541900</v>
+        <v>538200</v>
       </c>
       <c r="H27" s="3">
-        <v>1186000</v>
+        <v>1178000</v>
       </c>
       <c r="I27" s="3">
-        <v>959700</v>
+        <v>953200</v>
       </c>
       <c r="J27" s="3">
-        <v>1096800</v>
+        <v>1089300</v>
       </c>
       <c r="K27" s="3">
         <v>595700</v>
@@ -1545,10 +1545,10 @@
         <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>29400</v>
+        <v>29200</v>
       </c>
       <c r="J29" s="3">
-        <v>-348200</v>
+        <v>-345800</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1655,26 +1655,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-46500</v>
       </c>
       <c r="E32" s="3">
-        <v>-51100</v>
+        <v>-50800</v>
       </c>
       <c r="F32" s="3">
-        <v>-31600</v>
+        <v>-31300</v>
       </c>
       <c r="G32" s="3">
-        <v>-19600</v>
+        <v>-19500</v>
       </c>
       <c r="H32" s="3">
-        <v>-46800</v>
+        <v>-46500</v>
       </c>
       <c r="I32" s="3">
-        <v>-42400</v>
+        <v>-42100</v>
       </c>
       <c r="J32" s="3">
-        <v>-43500</v>
+        <v>-43200</v>
       </c>
       <c r="K32" s="3">
         <v>-14100</v>
@@ -1697,26 +1697,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>1803700</v>
       </c>
       <c r="E33" s="3">
-        <v>1640900</v>
+        <v>1629700</v>
       </c>
       <c r="F33" s="3">
-        <v>1068500</v>
+        <v>1061200</v>
       </c>
       <c r="G33" s="3">
-        <v>541900</v>
+        <v>538200</v>
       </c>
       <c r="H33" s="3">
-        <v>1186000</v>
+        <v>1178000</v>
       </c>
       <c r="I33" s="3">
-        <v>989100</v>
+        <v>982400</v>
       </c>
       <c r="J33" s="3">
-        <v>748600</v>
+        <v>743500</v>
       </c>
       <c r="K33" s="3">
         <v>595700</v>
@@ -1781,26 +1781,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>1803700</v>
       </c>
       <c r="E35" s="3">
-        <v>1640900</v>
+        <v>1629700</v>
       </c>
       <c r="F35" s="3">
-        <v>1068500</v>
+        <v>1061200</v>
       </c>
       <c r="G35" s="3">
-        <v>541900</v>
+        <v>538200</v>
       </c>
       <c r="H35" s="3">
-        <v>1186000</v>
+        <v>1178000</v>
       </c>
       <c r="I35" s="3">
-        <v>989100</v>
+        <v>982400</v>
       </c>
       <c r="J35" s="3">
-        <v>748600</v>
+        <v>743500</v>
       </c>
       <c r="K35" s="3">
         <v>595700</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1544000</v>
+        <v>502500</v>
       </c>
       <c r="E41" s="3">
-        <v>534300</v>
+        <v>530600</v>
       </c>
       <c r="F41" s="3">
-        <v>770400</v>
+        <v>765100</v>
       </c>
       <c r="G41" s="3">
-        <v>699600</v>
+        <v>694900</v>
       </c>
       <c r="H41" s="3">
-        <v>185000</v>
+        <v>183700</v>
       </c>
       <c r="I41" s="3">
-        <v>303600</v>
+        <v>301500</v>
       </c>
       <c r="J41" s="3">
-        <v>330800</v>
+        <v>328500</v>
       </c>
       <c r="K41" s="3">
         <v>302700</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>618000</v>
+        <v>1644800</v>
       </c>
       <c r="E42" s="3">
-        <v>1253500</v>
+        <v>1245000</v>
       </c>
       <c r="F42" s="3">
-        <v>823700</v>
+        <v>818100</v>
       </c>
       <c r="G42" s="3">
-        <v>957500</v>
+        <v>951000</v>
       </c>
       <c r="H42" s="3">
-        <v>158900</v>
+        <v>157800</v>
       </c>
       <c r="I42" s="3">
-        <v>32600</v>
+        <v>32400</v>
       </c>
       <c r="J42" s="3">
-        <v>60900</v>
+        <v>60500</v>
       </c>
       <c r="K42" s="3">
         <v>116100</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2968300</v>
+        <v>2948100</v>
       </c>
       <c r="E43" s="3">
-        <v>2927000</v>
+        <v>2907100</v>
       </c>
       <c r="F43" s="3">
-        <v>2713700</v>
+        <v>2695300</v>
       </c>
       <c r="G43" s="3">
-        <v>1749700</v>
+        <v>1737800</v>
       </c>
       <c r="H43" s="3">
-        <v>2142500</v>
+        <v>2127900</v>
       </c>
       <c r="I43" s="3">
-        <v>2082600</v>
+        <v>2068500</v>
       </c>
       <c r="J43" s="3">
-        <v>2425400</v>
+        <v>2408900</v>
       </c>
       <c r="K43" s="3">
         <v>2462900</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1475500</v>
+        <v>1465400</v>
       </c>
       <c r="E44" s="3">
-        <v>1501600</v>
+        <v>1491400</v>
       </c>
       <c r="F44" s="3">
-        <v>1258900</v>
+        <v>1250400</v>
       </c>
       <c r="G44" s="3">
-        <v>741000</v>
+        <v>736000</v>
       </c>
       <c r="H44" s="3">
-        <v>786700</v>
+        <v>781300</v>
       </c>
       <c r="I44" s="3">
-        <v>754100</v>
+        <v>748900</v>
       </c>
       <c r="J44" s="3">
-        <v>707300</v>
+        <v>702500</v>
       </c>
       <c r="K44" s="3">
         <v>730200</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>581000</v>
+        <v>577100</v>
       </c>
       <c r="E45" s="3">
-        <v>903100</v>
+        <v>897000</v>
       </c>
       <c r="F45" s="3">
-        <v>700700</v>
+        <v>696000</v>
       </c>
       <c r="G45" s="3">
-        <v>287300</v>
+        <v>285300</v>
       </c>
       <c r="H45" s="3">
-        <v>103400</v>
+        <v>102700</v>
       </c>
       <c r="I45" s="3">
-        <v>81600</v>
+        <v>81100</v>
       </c>
       <c r="J45" s="3">
-        <v>81600</v>
+        <v>81100</v>
       </c>
       <c r="K45" s="3">
         <v>104200</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7186900</v>
+        <v>7138000</v>
       </c>
       <c r="E46" s="3">
-        <v>7119400</v>
+        <v>7071000</v>
       </c>
       <c r="F46" s="3">
-        <v>6267500</v>
+        <v>6224800</v>
       </c>
       <c r="G46" s="3">
-        <v>4435100</v>
+        <v>4404900</v>
       </c>
       <c r="H46" s="3">
-        <v>3376400</v>
+        <v>3353400</v>
       </c>
       <c r="I46" s="3">
-        <v>3254500</v>
+        <v>3232400</v>
       </c>
       <c r="J46" s="3">
-        <v>3606000</v>
+        <v>3581400</v>
       </c>
       <c r="K46" s="3">
         <v>3716100</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5814800</v>
+        <v>5775300</v>
       </c>
       <c r="E48" s="3">
-        <v>5659200</v>
+        <v>5620700</v>
       </c>
       <c r="F48" s="3">
-        <v>5710300</v>
+        <v>5671500</v>
       </c>
       <c r="G48" s="3">
-        <v>4200100</v>
+        <v>4171500</v>
       </c>
       <c r="H48" s="3">
-        <v>4575500</v>
+        <v>4544300</v>
       </c>
       <c r="I48" s="3">
-        <v>4230500</v>
+        <v>4201800</v>
       </c>
       <c r="J48" s="3">
-        <v>4175000</v>
+        <v>4146600</v>
       </c>
       <c r="K48" s="3">
         <v>4332400</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18398700</v>
+        <v>18273600</v>
       </c>
       <c r="E49" s="3">
-        <v>18612000</v>
+        <v>18485400</v>
       </c>
       <c r="F49" s="3">
-        <v>18782800</v>
+        <v>18655000</v>
       </c>
       <c r="G49" s="3">
-        <v>11894000</v>
+        <v>11813100</v>
       </c>
       <c r="H49" s="3">
-        <v>11997400</v>
+        <v>11915800</v>
       </c>
       <c r="I49" s="3">
-        <v>11862500</v>
+        <v>11781800</v>
       </c>
       <c r="J49" s="3">
-        <v>11864600</v>
+        <v>11784000</v>
       </c>
       <c r="K49" s="3">
         <v>11686500</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>430900</v>
+        <v>428000</v>
       </c>
       <c r="E52" s="3">
-        <v>504900</v>
+        <v>501400</v>
       </c>
       <c r="F52" s="3">
-        <v>892200</v>
+        <v>886200</v>
       </c>
       <c r="G52" s="3">
-        <v>402600</v>
+        <v>399900</v>
       </c>
       <c r="H52" s="3">
-        <v>381900</v>
+        <v>379300</v>
       </c>
       <c r="I52" s="3">
-        <v>473300</v>
+        <v>470100</v>
       </c>
       <c r="J52" s="3">
-        <v>151200</v>
+        <v>150200</v>
       </c>
       <c r="K52" s="3">
         <v>411200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31831300</v>
+        <v>31614800</v>
       </c>
       <c r="E54" s="3">
-        <v>31895500</v>
+        <v>31678600</v>
       </c>
       <c r="F54" s="3">
-        <v>31652800</v>
+        <v>31437600</v>
       </c>
       <c r="G54" s="3">
-        <v>20931800</v>
+        <v>20789400</v>
       </c>
       <c r="H54" s="3">
-        <v>20331100</v>
+        <v>20192900</v>
       </c>
       <c r="I54" s="3">
-        <v>19820800</v>
+        <v>19686000</v>
       </c>
       <c r="J54" s="3">
-        <v>19796900</v>
+        <v>19662300</v>
       </c>
       <c r="K54" s="3">
         <v>20146300</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5695100</v>
+        <v>2492100</v>
       </c>
       <c r="E57" s="3">
-        <v>2384000</v>
+        <v>2367800</v>
       </c>
       <c r="F57" s="3">
-        <v>1840000</v>
+        <v>1827500</v>
       </c>
       <c r="G57" s="3">
-        <v>1223000</v>
+        <v>1214700</v>
       </c>
       <c r="H57" s="3">
-        <v>1238300</v>
+        <v>1229800</v>
       </c>
       <c r="I57" s="3">
-        <v>1202400</v>
+        <v>1194200</v>
       </c>
       <c r="J57" s="3">
-        <v>1150100</v>
+        <v>1142300</v>
       </c>
       <c r="K57" s="3">
         <v>980800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1414500</v>
+        <v>1404900</v>
       </c>
       <c r="E58" s="3">
-        <v>1453700</v>
+        <v>1443800</v>
       </c>
       <c r="F58" s="3">
-        <v>1468900</v>
+        <v>1458900</v>
       </c>
       <c r="G58" s="3">
-        <v>875900</v>
+        <v>870000</v>
       </c>
       <c r="H58" s="3">
-        <v>869400</v>
+        <v>863500</v>
       </c>
       <c r="I58" s="3">
-        <v>534300</v>
+        <v>530600</v>
       </c>
       <c r="J58" s="3">
-        <v>298100</v>
+        <v>296100</v>
       </c>
       <c r="K58" s="3">
         <v>949400</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>809500</v>
+        <v>3968300</v>
       </c>
       <c r="E59" s="3">
-        <v>4119500</v>
+        <v>4091500</v>
       </c>
       <c r="F59" s="3">
-        <v>3320900</v>
+        <v>3298300</v>
       </c>
       <c r="G59" s="3">
-        <v>2405800</v>
+        <v>2389400</v>
       </c>
       <c r="H59" s="3">
-        <v>2369900</v>
+        <v>2353800</v>
       </c>
       <c r="I59" s="3">
-        <v>2389500</v>
+        <v>2373200</v>
       </c>
       <c r="J59" s="3">
-        <v>2128300</v>
+        <v>2113800</v>
       </c>
       <c r="K59" s="3">
         <v>2140700</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7919200</v>
+        <v>7865300</v>
       </c>
       <c r="E60" s="3">
-        <v>7957300</v>
+        <v>7903200</v>
       </c>
       <c r="F60" s="3">
-        <v>6629800</v>
+        <v>6584700</v>
       </c>
       <c r="G60" s="3">
-        <v>4504700</v>
+        <v>4474100</v>
       </c>
       <c r="H60" s="3">
-        <v>4477500</v>
+        <v>4447100</v>
       </c>
       <c r="I60" s="3">
-        <v>4126100</v>
+        <v>4098000</v>
       </c>
       <c r="J60" s="3">
-        <v>3576600</v>
+        <v>3552300</v>
       </c>
       <c r="K60" s="3">
         <v>4070900</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10985500</v>
+        <v>10910700</v>
       </c>
       <c r="E61" s="3">
-        <v>11502300</v>
+        <v>11424100</v>
       </c>
       <c r="F61" s="3">
-        <v>12828700</v>
+        <v>12741500</v>
       </c>
       <c r="G61" s="3">
-        <v>6944300</v>
+        <v>6897000</v>
       </c>
       <c r="H61" s="3">
-        <v>6117300</v>
+        <v>6075700</v>
       </c>
       <c r="I61" s="3">
-        <v>5578700</v>
+        <v>5540700</v>
       </c>
       <c r="J61" s="3">
-        <v>5956300</v>
+        <v>5915800</v>
       </c>
       <c r="K61" s="3">
         <v>6034800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4247900</v>
+        <v>4219100</v>
       </c>
       <c r="E62" s="3">
-        <v>4332800</v>
+        <v>4303300</v>
       </c>
       <c r="F62" s="3">
-        <v>4349100</v>
+        <v>4319600</v>
       </c>
       <c r="G62" s="3">
-        <v>2927000</v>
+        <v>2907100</v>
       </c>
       <c r="H62" s="3">
-        <v>3038000</v>
+        <v>3017300</v>
       </c>
       <c r="I62" s="3">
-        <v>2973800</v>
+        <v>2953600</v>
       </c>
       <c r="J62" s="3">
-        <v>2990100</v>
+        <v>2969800</v>
       </c>
       <c r="K62" s="3">
         <v>3030400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23152600</v>
+        <v>22995100</v>
       </c>
       <c r="E66" s="3">
-        <v>23792400</v>
+        <v>23630600</v>
       </c>
       <c r="F66" s="3">
-        <v>24000200</v>
+        <v>23837000</v>
       </c>
       <c r="G66" s="3">
-        <v>14376000</v>
+        <v>14278200</v>
       </c>
       <c r="H66" s="3">
-        <v>13632800</v>
+        <v>13540100</v>
       </c>
       <c r="I66" s="3">
-        <v>12678500</v>
+        <v>12592300</v>
       </c>
       <c r="J66" s="3">
-        <v>12522900</v>
+        <v>12437800</v>
       </c>
       <c r="K66" s="3">
         <v>13136100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8372900</v>
+        <v>9122200</v>
       </c>
       <c r="E72" s="3">
-        <v>8307600</v>
+        <v>8251100</v>
       </c>
       <c r="F72" s="3">
-        <v>7583000</v>
+        <v>7531400</v>
       </c>
       <c r="G72" s="3">
-        <v>6925800</v>
+        <v>6878700</v>
       </c>
       <c r="H72" s="3">
-        <v>6987800</v>
+        <v>6940300</v>
       </c>
       <c r="I72" s="3">
-        <v>7572100</v>
+        <v>7520600</v>
       </c>
       <c r="J72" s="3">
-        <v>7677600</v>
+        <v>7625400</v>
       </c>
       <c r="K72" s="3">
         <v>7335700</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8678700</v>
+        <v>8619700</v>
       </c>
       <c r="E76" s="3">
-        <v>8103100</v>
+        <v>8048000</v>
       </c>
       <c r="F76" s="3">
-        <v>7652600</v>
+        <v>7600600</v>
       </c>
       <c r="G76" s="3">
-        <v>6555800</v>
+        <v>6511200</v>
       </c>
       <c r="H76" s="3">
-        <v>6698300</v>
+        <v>6652800</v>
       </c>
       <c r="I76" s="3">
-        <v>7142300</v>
+        <v>7093700</v>
       </c>
       <c r="J76" s="3">
-        <v>7273900</v>
+        <v>7224500</v>
       </c>
       <c r="K76" s="3">
         <v>7010200</v>
@@ -3435,26 +3435,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>1803700</v>
       </c>
       <c r="E81" s="3">
-        <v>1640900</v>
+        <v>1629700</v>
       </c>
       <c r="F81" s="3">
-        <v>1068500</v>
+        <v>1061200</v>
       </c>
       <c r="G81" s="3">
-        <v>541900</v>
+        <v>538200</v>
       </c>
       <c r="H81" s="3">
-        <v>1186000</v>
+        <v>1178000</v>
       </c>
       <c r="I81" s="3">
-        <v>989100</v>
+        <v>982400</v>
       </c>
       <c r="J81" s="3">
-        <v>748600</v>
+        <v>743500</v>
       </c>
       <c r="K81" s="3">
         <v>595700</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>861800</v>
+        <v>855900</v>
       </c>
       <c r="E83" s="3">
-        <v>887900</v>
+        <v>881900</v>
       </c>
       <c r="F83" s="3">
-        <v>850900</v>
+        <v>845100</v>
       </c>
       <c r="G83" s="3">
-        <v>791000</v>
+        <v>785700</v>
       </c>
       <c r="H83" s="3">
-        <v>695300</v>
+        <v>690600</v>
       </c>
       <c r="I83" s="3">
-        <v>557100</v>
+        <v>553300</v>
       </c>
       <c r="J83" s="3">
-        <v>533200</v>
+        <v>529500</v>
       </c>
       <c r="K83" s="3">
         <v>403600</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3053200</v>
+        <v>3032400</v>
       </c>
       <c r="E89" s="3">
-        <v>3190300</v>
+        <v>3168600</v>
       </c>
       <c r="F89" s="3">
-        <v>2303500</v>
+        <v>2287800</v>
       </c>
       <c r="G89" s="3">
-        <v>1621300</v>
+        <v>1610200</v>
       </c>
       <c r="H89" s="3">
-        <v>2071700</v>
+        <v>2057700</v>
       </c>
       <c r="I89" s="3">
-        <v>1965100</v>
+        <v>1951700</v>
       </c>
       <c r="J89" s="3">
-        <v>1766000</v>
+        <v>1754000</v>
       </c>
       <c r="K89" s="3">
         <v>1349700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-731200</v>
+        <v>-726200</v>
       </c>
       <c r="E91" s="3">
-        <v>-544100</v>
+        <v>-540400</v>
       </c>
       <c r="F91" s="3">
-        <v>-379700</v>
+        <v>-377200</v>
       </c>
       <c r="G91" s="3">
-        <v>-378700</v>
+        <v>-376100</v>
       </c>
       <c r="H91" s="3">
-        <v>-550600</v>
+        <v>-546800</v>
       </c>
       <c r="I91" s="3">
-        <v>-571300</v>
+        <v>-567400</v>
       </c>
       <c r="J91" s="3">
-        <v>-526600</v>
+        <v>-523100</v>
       </c>
       <c r="K91" s="3">
         <v>-498000</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1019500</v>
+        <v>-1012600</v>
       </c>
       <c r="E94" s="3">
-        <v>-701800</v>
+        <v>-697100</v>
       </c>
       <c r="F94" s="3">
-        <v>-6098800</v>
+        <v>-6057300</v>
       </c>
       <c r="G94" s="3">
-        <v>-402600</v>
+        <v>-399900</v>
       </c>
       <c r="H94" s="3">
-        <v>-651800</v>
+        <v>-647300</v>
       </c>
       <c r="I94" s="3">
-        <v>-648500</v>
+        <v>-644100</v>
       </c>
       <c r="J94" s="3">
-        <v>-531000</v>
+        <v>-527400</v>
       </c>
       <c r="K94" s="3">
         <v>-415600</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-915100</v>
+        <v>-908900</v>
       </c>
       <c r="E96" s="3">
-        <v>-830200</v>
+        <v>-824600</v>
       </c>
       <c r="F96" s="3">
-        <v>-694200</v>
+        <v>-689500</v>
       </c>
       <c r="G96" s="3">
-        <v>-420000</v>
+        <v>-417200</v>
       </c>
       <c r="H96" s="3">
-        <v>-624600</v>
+        <v>-620300</v>
       </c>
       <c r="I96" s="3">
-        <v>-558200</v>
+        <v>-554400</v>
       </c>
       <c r="J96" s="3">
-        <v>-532100</v>
+        <v>-528500</v>
       </c>
       <c r="K96" s="3">
         <v>-221300</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1982500</v>
+        <v>-1969000</v>
       </c>
       <c r="E100" s="3">
-        <v>-2476500</v>
+        <v>-2459700</v>
       </c>
       <c r="F100" s="3">
-        <v>3578800</v>
+        <v>3554400</v>
       </c>
       <c r="G100" s="3">
-        <v>108800</v>
+        <v>108100</v>
       </c>
       <c r="H100" s="3">
-        <v>-1416700</v>
+        <v>-1407100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1369900</v>
+        <v>-1360600</v>
       </c>
       <c r="J100" s="3">
-        <v>-1253500</v>
+        <v>-1245000</v>
       </c>
       <c r="K100" s="3">
         <v>-679200</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-16300</v>
+        <v>-16200</v>
       </c>
       <c r="E101" s="3">
-        <v>-33700</v>
+        <v>-33500</v>
       </c>
       <c r="F101" s="3">
-        <v>90300</v>
+        <v>89700</v>
       </c>
       <c r="G101" s="3">
-        <v>-14100</v>
+        <v>-14000</v>
       </c>
       <c r="H101" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="I101" s="3">
         <v>-2200</v>
       </c>
       <c r="J101" s="3">
-        <v>-9800</v>
+        <v>-9700</v>
       </c>
       <c r="K101" s="3">
         <v>-5400</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-51100</v>
+        <v>34600</v>
       </c>
       <c r="E102" s="3">
-        <v>-21800</v>
+        <v>-21600</v>
       </c>
       <c r="F102" s="3">
-        <v>-126200</v>
+        <v>-125400</v>
       </c>
       <c r="G102" s="3">
-        <v>1313300</v>
+        <v>1304400</v>
       </c>
       <c r="H102" s="3">
         <v>7600</v>
       </c>
       <c r="I102" s="3">
-        <v>-55500</v>
+        <v>-55100</v>
       </c>
       <c r="J102" s="3">
-        <v>-28300</v>
+        <v>-28100</v>
       </c>
       <c r="K102" s="3">
         <v>249600</v>

--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19779000</v>
+        <v>20271300</v>
       </c>
       <c r="E8" s="3">
-        <v>18717700</v>
+        <v>19183600</v>
       </c>
       <c r="F8" s="3">
-        <v>14873700</v>
+        <v>15243900</v>
       </c>
       <c r="G8" s="3">
-        <v>11461900</v>
+        <v>11747200</v>
       </c>
       <c r="H8" s="3">
-        <v>12986800</v>
+        <v>13310000</v>
       </c>
       <c r="I8" s="3">
-        <v>12447500</v>
+        <v>12757300</v>
       </c>
       <c r="J8" s="3">
-        <v>11954700</v>
+        <v>12252300</v>
       </c>
       <c r="K8" s="3">
         <v>9909300</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12423700</v>
+        <v>12733000</v>
       </c>
       <c r="E9" s="3">
-        <v>11926600</v>
+        <v>12223500</v>
       </c>
       <c r="F9" s="3">
-        <v>9314600</v>
+        <v>9546400</v>
       </c>
       <c r="G9" s="3">
-        <v>7327100</v>
+        <v>7509500</v>
       </c>
       <c r="H9" s="3">
-        <v>7996100</v>
+        <v>8195100</v>
       </c>
       <c r="I9" s="3">
-        <v>7578900</v>
+        <v>7767600</v>
       </c>
       <c r="J9" s="3">
-        <v>7291500</v>
+        <v>7473000</v>
       </c>
       <c r="K9" s="3">
         <v>6058600</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7355200</v>
+        <v>7538300</v>
       </c>
       <c r="E10" s="3">
-        <v>6791100</v>
+        <v>6960200</v>
       </c>
       <c r="F10" s="3">
-        <v>5559100</v>
+        <v>5697500</v>
       </c>
       <c r="G10" s="3">
-        <v>4134800</v>
+        <v>4237700</v>
       </c>
       <c r="H10" s="3">
-        <v>4990700</v>
+        <v>5114900</v>
       </c>
       <c r="I10" s="3">
-        <v>4868600</v>
+        <v>4989700</v>
       </c>
       <c r="J10" s="3">
-        <v>4663200</v>
+        <v>4779300</v>
       </c>
       <c r="K10" s="3">
         <v>3850700</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>35700</v>
+        <v>36600</v>
       </c>
       <c r="E14" s="3">
-        <v>64800</v>
+        <v>66500</v>
       </c>
       <c r="F14" s="3">
-        <v>62700</v>
+        <v>64200</v>
       </c>
       <c r="G14" s="3">
-        <v>98300</v>
+        <v>100800</v>
       </c>
       <c r="H14" s="3">
-        <v>27000</v>
+        <v>27700</v>
       </c>
       <c r="I14" s="3">
-        <v>50800</v>
+        <v>52100</v>
       </c>
       <c r="J14" s="3">
-        <v>27000</v>
+        <v>27700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>112400</v>
+        <v>115200</v>
       </c>
       <c r="E15" s="3">
-        <v>100500</v>
+        <v>103000</v>
       </c>
       <c r="F15" s="3">
-        <v>90800</v>
+        <v>93000</v>
       </c>
       <c r="G15" s="3">
-        <v>67000</v>
+        <v>68700</v>
       </c>
       <c r="H15" s="3">
+        <v>48700</v>
+      </c>
+      <c r="I15" s="3">
         <v>47600</v>
       </c>
-      <c r="I15" s="3">
-        <v>46500</v>
-      </c>
       <c r="J15" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="K15" s="3">
         <v>35800</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17251200</v>
+        <v>17680600</v>
       </c>
       <c r="E17" s="3">
-        <v>16463400</v>
+        <v>16873200</v>
       </c>
       <c r="F17" s="3">
-        <v>13235300</v>
+        <v>13564800</v>
       </c>
       <c r="G17" s="3">
-        <v>10583300</v>
+        <v>10846700</v>
       </c>
       <c r="H17" s="3">
-        <v>11313800</v>
+        <v>11595500</v>
       </c>
       <c r="I17" s="3">
-        <v>11042600</v>
+        <v>11317500</v>
       </c>
       <c r="J17" s="3">
-        <v>10593000</v>
+        <v>10856700</v>
       </c>
       <c r="K17" s="3">
         <v>8986000</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2527800</v>
+        <v>2590700</v>
       </c>
       <c r="E18" s="3">
-        <v>2254300</v>
+        <v>2310500</v>
       </c>
       <c r="F18" s="3">
-        <v>1638300</v>
+        <v>1679100</v>
       </c>
       <c r="G18" s="3">
-        <v>878600</v>
+        <v>900500</v>
       </c>
       <c r="H18" s="3">
-        <v>1672900</v>
+        <v>1714600</v>
       </c>
       <c r="I18" s="3">
-        <v>1404900</v>
+        <v>1439900</v>
       </c>
       <c r="J18" s="3">
-        <v>1361700</v>
+        <v>1395600</v>
       </c>
       <c r="K18" s="3">
         <v>923300</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>46500</v>
+        <v>47600</v>
       </c>
       <c r="E20" s="3">
-        <v>50800</v>
+        <v>52100</v>
       </c>
       <c r="F20" s="3">
-        <v>31300</v>
+        <v>32100</v>
       </c>
       <c r="G20" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="H20" s="3">
-        <v>46500</v>
+        <v>47600</v>
       </c>
       <c r="I20" s="3">
-        <v>42100</v>
+        <v>43200</v>
       </c>
       <c r="J20" s="3">
-        <v>43200</v>
+        <v>44300</v>
       </c>
       <c r="K20" s="3">
         <v>14100</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3424700</v>
+        <v>3515400</v>
       </c>
       <c r="E21" s="3">
-        <v>3181400</v>
+        <v>3266100</v>
       </c>
       <c r="F21" s="3">
-        <v>2509500</v>
+        <v>2577200</v>
       </c>
       <c r="G21" s="3">
-        <v>1678800</v>
+        <v>1725500</v>
       </c>
       <c r="H21" s="3">
-        <v>2405600</v>
+        <v>2469800</v>
       </c>
       <c r="I21" s="3">
-        <v>1996900</v>
+        <v>2050100</v>
       </c>
       <c r="J21" s="3">
-        <v>1931100</v>
+        <v>1982500</v>
       </c>
       <c r="K21" s="3">
         <v>1340900</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>193400</v>
+        <v>198300</v>
       </c>
       <c r="E22" s="3">
-        <v>190200</v>
+        <v>194900</v>
       </c>
       <c r="F22" s="3">
-        <v>176200</v>
+        <v>180500</v>
       </c>
       <c r="G22" s="3">
-        <v>147000</v>
+        <v>150600</v>
       </c>
       <c r="H22" s="3">
-        <v>148100</v>
+        <v>151700</v>
       </c>
       <c r="I22" s="3">
-        <v>144800</v>
+        <v>148400</v>
       </c>
       <c r="J22" s="3">
-        <v>152400</v>
+        <v>156200</v>
       </c>
       <c r="K22" s="3">
         <v>157300</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2380800</v>
+        <v>2440000</v>
       </c>
       <c r="E23" s="3">
-        <v>2114900</v>
+        <v>2167600</v>
       </c>
       <c r="F23" s="3">
-        <v>1493500</v>
+        <v>1530700</v>
       </c>
       <c r="G23" s="3">
-        <v>751100</v>
+        <v>769800</v>
       </c>
       <c r="H23" s="3">
-        <v>1571300</v>
+        <v>1610500</v>
       </c>
       <c r="I23" s="3">
-        <v>1302200</v>
+        <v>1334700</v>
       </c>
       <c r="J23" s="3">
-        <v>1252500</v>
+        <v>1283700</v>
       </c>
       <c r="K23" s="3">
         <v>780100</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>577100</v>
+        <v>591500</v>
       </c>
       <c r="E24" s="3">
-        <v>471200</v>
+        <v>482900</v>
       </c>
       <c r="F24" s="3">
-        <v>425800</v>
+        <v>436400</v>
       </c>
       <c r="G24" s="3">
-        <v>212900</v>
+        <v>218200</v>
       </c>
       <c r="H24" s="3">
-        <v>393400</v>
+        <v>403200</v>
       </c>
       <c r="I24" s="3">
-        <v>349100</v>
+        <v>357800</v>
       </c>
       <c r="J24" s="3">
-        <v>163200</v>
+        <v>167200</v>
       </c>
       <c r="K24" s="3">
         <v>184500</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1803700</v>
+        <v>1848600</v>
       </c>
       <c r="E26" s="3">
-        <v>1643700</v>
+        <v>1684700</v>
       </c>
       <c r="F26" s="3">
-        <v>1067700</v>
+        <v>1094300</v>
       </c>
       <c r="G26" s="3">
-        <v>538200</v>
+        <v>551600</v>
       </c>
       <c r="H26" s="3">
-        <v>1178000</v>
+        <v>1207300</v>
       </c>
       <c r="I26" s="3">
-        <v>953200</v>
+        <v>976900</v>
       </c>
       <c r="J26" s="3">
-        <v>1089300</v>
+        <v>1116500</v>
       </c>
       <c r="K26" s="3">
         <v>595700</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1803700</v>
+        <v>1848600</v>
       </c>
       <c r="E27" s="3">
-        <v>1629700</v>
+        <v>1670300</v>
       </c>
       <c r="F27" s="3">
-        <v>1061200</v>
+        <v>1087700</v>
       </c>
       <c r="G27" s="3">
-        <v>538200</v>
+        <v>551600</v>
       </c>
       <c r="H27" s="3">
-        <v>1178000</v>
+        <v>1207300</v>
       </c>
       <c r="I27" s="3">
-        <v>953200</v>
+        <v>976900</v>
       </c>
       <c r="J27" s="3">
-        <v>1089300</v>
+        <v>1116500</v>
       </c>
       <c r="K27" s="3">
         <v>595700</v>
@@ -1545,10 +1545,10 @@
         <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>29200</v>
+        <v>29900</v>
       </c>
       <c r="J29" s="3">
-        <v>-345800</v>
+        <v>-354400</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-46500</v>
+        <v>-47600</v>
       </c>
       <c r="E32" s="3">
-        <v>-50800</v>
+        <v>-52100</v>
       </c>
       <c r="F32" s="3">
-        <v>-31300</v>
+        <v>-32100</v>
       </c>
       <c r="G32" s="3">
-        <v>-19500</v>
+        <v>-19900</v>
       </c>
       <c r="H32" s="3">
-        <v>-46500</v>
+        <v>-47600</v>
       </c>
       <c r="I32" s="3">
-        <v>-42100</v>
+        <v>-43200</v>
       </c>
       <c r="J32" s="3">
-        <v>-43200</v>
+        <v>-44300</v>
       </c>
       <c r="K32" s="3">
         <v>-14100</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1803700</v>
+        <v>1848600</v>
       </c>
       <c r="E33" s="3">
-        <v>1629700</v>
+        <v>1670300</v>
       </c>
       <c r="F33" s="3">
-        <v>1061200</v>
+        <v>1087700</v>
       </c>
       <c r="G33" s="3">
-        <v>538200</v>
+        <v>551600</v>
       </c>
       <c r="H33" s="3">
-        <v>1178000</v>
+        <v>1207300</v>
       </c>
       <c r="I33" s="3">
-        <v>982400</v>
+        <v>1006800</v>
       </c>
       <c r="J33" s="3">
-        <v>743500</v>
+        <v>762000</v>
       </c>
       <c r="K33" s="3">
         <v>595700</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1803700</v>
+        <v>1848600</v>
       </c>
       <c r="E35" s="3">
-        <v>1629700</v>
+        <v>1670300</v>
       </c>
       <c r="F35" s="3">
-        <v>1061200</v>
+        <v>1087700</v>
       </c>
       <c r="G35" s="3">
-        <v>538200</v>
+        <v>551600</v>
       </c>
       <c r="H35" s="3">
-        <v>1178000</v>
+        <v>1207300</v>
       </c>
       <c r="I35" s="3">
-        <v>982400</v>
+        <v>1006800</v>
       </c>
       <c r="J35" s="3">
-        <v>743500</v>
+        <v>762000</v>
       </c>
       <c r="K35" s="3">
         <v>595700</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>502500</v>
+        <v>515000</v>
       </c>
       <c r="E41" s="3">
-        <v>530600</v>
+        <v>543800</v>
       </c>
       <c r="F41" s="3">
-        <v>765100</v>
+        <v>784200</v>
       </c>
       <c r="G41" s="3">
-        <v>694900</v>
+        <v>712200</v>
       </c>
       <c r="H41" s="3">
-        <v>183700</v>
+        <v>188300</v>
       </c>
       <c r="I41" s="3">
-        <v>301500</v>
+        <v>309000</v>
       </c>
       <c r="J41" s="3">
-        <v>328500</v>
+        <v>336700</v>
       </c>
       <c r="K41" s="3">
         <v>302700</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1644800</v>
+        <v>1685800</v>
       </c>
       <c r="E42" s="3">
-        <v>1245000</v>
+        <v>1276000</v>
       </c>
       <c r="F42" s="3">
-        <v>818100</v>
+        <v>838500</v>
       </c>
       <c r="G42" s="3">
-        <v>951000</v>
+        <v>974700</v>
       </c>
       <c r="H42" s="3">
-        <v>157800</v>
+        <v>161700</v>
       </c>
       <c r="I42" s="3">
-        <v>32400</v>
+        <v>33200</v>
       </c>
       <c r="J42" s="3">
-        <v>60500</v>
+        <v>62000</v>
       </c>
       <c r="K42" s="3">
         <v>116100</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2948100</v>
+        <v>3021500</v>
       </c>
       <c r="E43" s="3">
-        <v>2907100</v>
+        <v>2979400</v>
       </c>
       <c r="F43" s="3">
-        <v>2695300</v>
+        <v>2762400</v>
       </c>
       <c r="G43" s="3">
-        <v>1737800</v>
+        <v>1781000</v>
       </c>
       <c r="H43" s="3">
-        <v>2127900</v>
+        <v>2180900</v>
       </c>
       <c r="I43" s="3">
-        <v>2068500</v>
+        <v>2119900</v>
       </c>
       <c r="J43" s="3">
-        <v>2408900</v>
+        <v>2468800</v>
       </c>
       <c r="K43" s="3">
         <v>2462900</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1465400</v>
+        <v>1501900</v>
       </c>
       <c r="E44" s="3">
-        <v>1491400</v>
+        <v>1528500</v>
       </c>
       <c r="F44" s="3">
-        <v>1250400</v>
+        <v>1281500</v>
       </c>
       <c r="G44" s="3">
-        <v>736000</v>
+        <v>754300</v>
       </c>
       <c r="H44" s="3">
-        <v>781300</v>
+        <v>800800</v>
       </c>
       <c r="I44" s="3">
-        <v>748900</v>
+        <v>767600</v>
       </c>
       <c r="J44" s="3">
-        <v>702500</v>
+        <v>719900</v>
       </c>
       <c r="K44" s="3">
         <v>730200</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>577100</v>
+        <v>591500</v>
       </c>
       <c r="E45" s="3">
-        <v>897000</v>
+        <v>919300</v>
       </c>
       <c r="F45" s="3">
-        <v>696000</v>
+        <v>713300</v>
       </c>
       <c r="G45" s="3">
-        <v>285300</v>
+        <v>292400</v>
       </c>
       <c r="H45" s="3">
-        <v>102700</v>
+        <v>105200</v>
       </c>
       <c r="I45" s="3">
-        <v>81100</v>
+        <v>83100</v>
       </c>
       <c r="J45" s="3">
-        <v>81100</v>
+        <v>83100</v>
       </c>
       <c r="K45" s="3">
         <v>104200</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7138000</v>
+        <v>7315700</v>
       </c>
       <c r="E46" s="3">
-        <v>7071000</v>
+        <v>7247000</v>
       </c>
       <c r="F46" s="3">
-        <v>6224800</v>
+        <v>6379800</v>
       </c>
       <c r="G46" s="3">
-        <v>4404900</v>
+        <v>4514600</v>
       </c>
       <c r="H46" s="3">
-        <v>3353400</v>
+        <v>3436900</v>
       </c>
       <c r="I46" s="3">
-        <v>3232400</v>
+        <v>3312800</v>
       </c>
       <c r="J46" s="3">
-        <v>3581400</v>
+        <v>3670600</v>
       </c>
       <c r="K46" s="3">
         <v>3716100</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5775300</v>
+        <v>5919000</v>
       </c>
       <c r="E48" s="3">
-        <v>5620700</v>
+        <v>5760600</v>
       </c>
       <c r="F48" s="3">
-        <v>5671500</v>
+        <v>5812700</v>
       </c>
       <c r="G48" s="3">
-        <v>4171500</v>
+        <v>4275300</v>
       </c>
       <c r="H48" s="3">
-        <v>4544300</v>
+        <v>4657500</v>
       </c>
       <c r="I48" s="3">
-        <v>4201800</v>
+        <v>4306300</v>
       </c>
       <c r="J48" s="3">
-        <v>4146600</v>
+        <v>4249900</v>
       </c>
       <c r="K48" s="3">
         <v>4332400</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18273600</v>
+        <v>18728400</v>
       </c>
       <c r="E49" s="3">
-        <v>18485400</v>
+        <v>18945500</v>
       </c>
       <c r="F49" s="3">
-        <v>18655000</v>
+        <v>19119400</v>
       </c>
       <c r="G49" s="3">
-        <v>11813100</v>
+        <v>12107200</v>
       </c>
       <c r="H49" s="3">
-        <v>11915800</v>
+        <v>12212400</v>
       </c>
       <c r="I49" s="3">
-        <v>11781800</v>
+        <v>12075100</v>
       </c>
       <c r="J49" s="3">
-        <v>11784000</v>
+        <v>12077300</v>
       </c>
       <c r="K49" s="3">
         <v>11686500</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>428000</v>
+        <v>438600</v>
       </c>
       <c r="E52" s="3">
-        <v>501400</v>
+        <v>513900</v>
       </c>
       <c r="F52" s="3">
-        <v>886200</v>
+        <v>908200</v>
       </c>
       <c r="G52" s="3">
-        <v>399900</v>
+        <v>409800</v>
       </c>
       <c r="H52" s="3">
-        <v>379300</v>
+        <v>388800</v>
       </c>
       <c r="I52" s="3">
-        <v>470100</v>
+        <v>481800</v>
       </c>
       <c r="J52" s="3">
-        <v>150200</v>
+        <v>154000</v>
       </c>
       <c r="K52" s="3">
         <v>411200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31614800</v>
+        <v>32401700</v>
       </c>
       <c r="E54" s="3">
-        <v>31678600</v>
+        <v>32467100</v>
       </c>
       <c r="F54" s="3">
-        <v>31437600</v>
+        <v>32220100</v>
       </c>
       <c r="G54" s="3">
-        <v>20789400</v>
+        <v>21306900</v>
       </c>
       <c r="H54" s="3">
-        <v>20192900</v>
+        <v>20695500</v>
       </c>
       <c r="I54" s="3">
-        <v>19686000</v>
+        <v>20176000</v>
       </c>
       <c r="J54" s="3">
-        <v>19662300</v>
+        <v>20151700</v>
       </c>
       <c r="K54" s="3">
         <v>20146300</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2492100</v>
+        <v>2554100</v>
       </c>
       <c r="E57" s="3">
-        <v>2367800</v>
+        <v>2426800</v>
       </c>
       <c r="F57" s="3">
-        <v>1827500</v>
+        <v>1873000</v>
       </c>
       <c r="G57" s="3">
-        <v>1214700</v>
+        <v>1244900</v>
       </c>
       <c r="H57" s="3">
-        <v>1229800</v>
+        <v>1260400</v>
       </c>
       <c r="I57" s="3">
-        <v>1194200</v>
+        <v>1223900</v>
       </c>
       <c r="J57" s="3">
-        <v>1142300</v>
+        <v>1170700</v>
       </c>
       <c r="K57" s="3">
         <v>980800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1404900</v>
+        <v>1439900</v>
       </c>
       <c r="E58" s="3">
-        <v>1443800</v>
+        <v>1479800</v>
       </c>
       <c r="F58" s="3">
-        <v>1458900</v>
+        <v>1495300</v>
       </c>
       <c r="G58" s="3">
-        <v>870000</v>
+        <v>891600</v>
       </c>
       <c r="H58" s="3">
-        <v>863500</v>
+        <v>885000</v>
       </c>
       <c r="I58" s="3">
-        <v>530600</v>
+        <v>543800</v>
       </c>
       <c r="J58" s="3">
-        <v>296100</v>
+        <v>303500</v>
       </c>
       <c r="K58" s="3">
         <v>949400</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3968300</v>
+        <v>4067100</v>
       </c>
       <c r="E59" s="3">
-        <v>4091500</v>
+        <v>4193400</v>
       </c>
       <c r="F59" s="3">
-        <v>3298300</v>
+        <v>3380400</v>
       </c>
       <c r="G59" s="3">
-        <v>2389400</v>
+        <v>2448900</v>
       </c>
       <c r="H59" s="3">
-        <v>2353800</v>
+        <v>2412400</v>
       </c>
       <c r="I59" s="3">
-        <v>2373200</v>
+        <v>2432300</v>
       </c>
       <c r="J59" s="3">
-        <v>2113800</v>
+        <v>2166500</v>
       </c>
       <c r="K59" s="3">
         <v>2140700</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7865300</v>
+        <v>8061100</v>
       </c>
       <c r="E60" s="3">
-        <v>7903200</v>
+        <v>8099900</v>
       </c>
       <c r="F60" s="3">
-        <v>6584700</v>
+        <v>6748600</v>
       </c>
       <c r="G60" s="3">
-        <v>4474100</v>
+        <v>4585500</v>
       </c>
       <c r="H60" s="3">
-        <v>4447100</v>
+        <v>4557800</v>
       </c>
       <c r="I60" s="3">
-        <v>4098000</v>
+        <v>4200000</v>
       </c>
       <c r="J60" s="3">
-        <v>3552300</v>
+        <v>3640700</v>
       </c>
       <c r="K60" s="3">
         <v>4070900</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10910700</v>
+        <v>11182300</v>
       </c>
       <c r="E61" s="3">
-        <v>11424100</v>
+        <v>11708400</v>
       </c>
       <c r="F61" s="3">
-        <v>12741500</v>
+        <v>13058600</v>
       </c>
       <c r="G61" s="3">
-        <v>6897000</v>
+        <v>7068700</v>
       </c>
       <c r="H61" s="3">
-        <v>6075700</v>
+        <v>6226900</v>
       </c>
       <c r="I61" s="3">
-        <v>5540700</v>
+        <v>5678700</v>
       </c>
       <c r="J61" s="3">
-        <v>5915800</v>
+        <v>6063000</v>
       </c>
       <c r="K61" s="3">
         <v>6034800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4219100</v>
+        <v>4324100</v>
       </c>
       <c r="E62" s="3">
-        <v>4303300</v>
+        <v>4410500</v>
       </c>
       <c r="F62" s="3">
-        <v>4319600</v>
+        <v>4427100</v>
       </c>
       <c r="G62" s="3">
-        <v>2907100</v>
+        <v>2979400</v>
       </c>
       <c r="H62" s="3">
-        <v>3017300</v>
+        <v>3092400</v>
       </c>
       <c r="I62" s="3">
-        <v>2953600</v>
+        <v>3027100</v>
       </c>
       <c r="J62" s="3">
-        <v>2969800</v>
+        <v>3043700</v>
       </c>
       <c r="K62" s="3">
         <v>3030400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>22995100</v>
+        <v>23567500</v>
       </c>
       <c r="E66" s="3">
-        <v>23630600</v>
+        <v>24218800</v>
       </c>
       <c r="F66" s="3">
-        <v>23837000</v>
+        <v>24430300</v>
       </c>
       <c r="G66" s="3">
-        <v>14278200</v>
+        <v>14633600</v>
       </c>
       <c r="H66" s="3">
-        <v>13540100</v>
+        <v>13877100</v>
       </c>
       <c r="I66" s="3">
-        <v>12592300</v>
+        <v>12905800</v>
       </c>
       <c r="J66" s="3">
-        <v>12437800</v>
+        <v>12747400</v>
       </c>
       <c r="K66" s="3">
         <v>13136100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9122200</v>
+        <v>9349300</v>
       </c>
       <c r="E72" s="3">
-        <v>8251100</v>
+        <v>8456500</v>
       </c>
       <c r="F72" s="3">
-        <v>7531400</v>
+        <v>7718900</v>
       </c>
       <c r="G72" s="3">
-        <v>6878700</v>
+        <v>7049900</v>
       </c>
       <c r="H72" s="3">
-        <v>6940300</v>
+        <v>7113000</v>
       </c>
       <c r="I72" s="3">
-        <v>7520600</v>
+        <v>7707800</v>
       </c>
       <c r="J72" s="3">
-        <v>7625400</v>
+        <v>7815200</v>
       </c>
       <c r="K72" s="3">
         <v>7335700</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8619700</v>
+        <v>8834200</v>
       </c>
       <c r="E76" s="3">
-        <v>8048000</v>
+        <v>8248300</v>
       </c>
       <c r="F76" s="3">
-        <v>7600600</v>
+        <v>7789800</v>
       </c>
       <c r="G76" s="3">
-        <v>6511200</v>
+        <v>6673300</v>
       </c>
       <c r="H76" s="3">
-        <v>6652800</v>
+        <v>6818400</v>
       </c>
       <c r="I76" s="3">
-        <v>7093700</v>
+        <v>7270300</v>
       </c>
       <c r="J76" s="3">
-        <v>7224500</v>
+        <v>7404300</v>
       </c>
       <c r="K76" s="3">
         <v>7010200</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1803700</v>
+        <v>1848600</v>
       </c>
       <c r="E81" s="3">
-        <v>1629700</v>
+        <v>1670300</v>
       </c>
       <c r="F81" s="3">
-        <v>1061200</v>
+        <v>1087700</v>
       </c>
       <c r="G81" s="3">
-        <v>538200</v>
+        <v>551600</v>
       </c>
       <c r="H81" s="3">
-        <v>1178000</v>
+        <v>1207300</v>
       </c>
       <c r="I81" s="3">
-        <v>982400</v>
+        <v>1006800</v>
       </c>
       <c r="J81" s="3">
-        <v>743500</v>
+        <v>762000</v>
       </c>
       <c r="K81" s="3">
         <v>595700</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>855900</v>
+        <v>877200</v>
       </c>
       <c r="E83" s="3">
-        <v>881900</v>
+        <v>903800</v>
       </c>
       <c r="F83" s="3">
-        <v>845100</v>
+        <v>866100</v>
       </c>
       <c r="G83" s="3">
-        <v>785700</v>
+        <v>805200</v>
       </c>
       <c r="H83" s="3">
-        <v>690600</v>
+        <v>707800</v>
       </c>
       <c r="I83" s="3">
-        <v>553300</v>
+        <v>567100</v>
       </c>
       <c r="J83" s="3">
-        <v>529500</v>
+        <v>542700</v>
       </c>
       <c r="K83" s="3">
         <v>403600</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3032400</v>
+        <v>3107900</v>
       </c>
       <c r="E89" s="3">
-        <v>3168600</v>
+        <v>3247500</v>
       </c>
       <c r="F89" s="3">
-        <v>2287800</v>
+        <v>2344800</v>
       </c>
       <c r="G89" s="3">
-        <v>1610200</v>
+        <v>1650300</v>
       </c>
       <c r="H89" s="3">
-        <v>2057700</v>
+        <v>2108900</v>
       </c>
       <c r="I89" s="3">
-        <v>1951700</v>
+        <v>2000300</v>
       </c>
       <c r="J89" s="3">
-        <v>1754000</v>
+        <v>1797600</v>
       </c>
       <c r="K89" s="3">
         <v>1349700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-726200</v>
+        <v>-744300</v>
       </c>
       <c r="E91" s="3">
-        <v>-540400</v>
+        <v>-553800</v>
       </c>
       <c r="F91" s="3">
-        <v>-377200</v>
+        <v>-386600</v>
       </c>
       <c r="G91" s="3">
-        <v>-376100</v>
+        <v>-385400</v>
       </c>
       <c r="H91" s="3">
-        <v>-546800</v>
+        <v>-560400</v>
       </c>
       <c r="I91" s="3">
-        <v>-567400</v>
+        <v>-581500</v>
       </c>
       <c r="J91" s="3">
-        <v>-523100</v>
+        <v>-536100</v>
       </c>
       <c r="K91" s="3">
         <v>-498000</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1012600</v>
+        <v>-1037800</v>
       </c>
       <c r="E94" s="3">
-        <v>-697100</v>
+        <v>-714400</v>
       </c>
       <c r="F94" s="3">
-        <v>-6057300</v>
+        <v>-6208100</v>
       </c>
       <c r="G94" s="3">
-        <v>-399900</v>
+        <v>-409800</v>
       </c>
       <c r="H94" s="3">
-        <v>-647300</v>
+        <v>-663500</v>
       </c>
       <c r="I94" s="3">
-        <v>-644100</v>
+        <v>-660100</v>
       </c>
       <c r="J94" s="3">
-        <v>-527400</v>
+        <v>-540500</v>
       </c>
       <c r="K94" s="3">
         <v>-415600</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-908900</v>
+        <v>-931500</v>
       </c>
       <c r="E96" s="3">
-        <v>-824600</v>
+        <v>-845100</v>
       </c>
       <c r="F96" s="3">
-        <v>-689500</v>
+        <v>-706600</v>
       </c>
       <c r="G96" s="3">
-        <v>-417200</v>
+        <v>-427500</v>
       </c>
       <c r="H96" s="3">
-        <v>-620300</v>
+        <v>-635800</v>
       </c>
       <c r="I96" s="3">
-        <v>-554400</v>
+        <v>-568200</v>
       </c>
       <c r="J96" s="3">
-        <v>-528500</v>
+        <v>-541600</v>
       </c>
       <c r="K96" s="3">
         <v>-221300</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1969000</v>
+        <v>-2018000</v>
       </c>
       <c r="E100" s="3">
-        <v>-2459700</v>
+        <v>-2520900</v>
       </c>
       <c r="F100" s="3">
-        <v>3554400</v>
+        <v>3642900</v>
       </c>
       <c r="G100" s="3">
-        <v>108100</v>
+        <v>110800</v>
       </c>
       <c r="H100" s="3">
-        <v>-1407100</v>
+        <v>-1442100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1360600</v>
+        <v>-1394500</v>
       </c>
       <c r="J100" s="3">
-        <v>-1245000</v>
+        <v>-1276000</v>
       </c>
       <c r="K100" s="3">
         <v>-679200</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-16200</v>
+        <v>-16600</v>
       </c>
       <c r="E101" s="3">
-        <v>-33500</v>
+        <v>-34300</v>
       </c>
       <c r="F101" s="3">
-        <v>89700</v>
+        <v>91900</v>
       </c>
       <c r="G101" s="3">
-        <v>-14000</v>
+        <v>-14400</v>
       </c>
       <c r="H101" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="I101" s="3">
         <v>-2200</v>
       </c>
       <c r="J101" s="3">
-        <v>-9700</v>
+        <v>-10000</v>
       </c>
       <c r="K101" s="3">
         <v>-5400</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>34600</v>
+        <v>35400</v>
       </c>
       <c r="E102" s="3">
-        <v>-21600</v>
+        <v>-22200</v>
       </c>
       <c r="F102" s="3">
-        <v>-125400</v>
+        <v>-128500</v>
       </c>
       <c r="G102" s="3">
-        <v>1304400</v>
+        <v>1336900</v>
       </c>
       <c r="H102" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="I102" s="3">
-        <v>-55100</v>
+        <v>-56500</v>
       </c>
       <c r="J102" s="3">
-        <v>-28100</v>
+        <v>-28800</v>
       </c>
       <c r="K102" s="3">
         <v>249600</v>

--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>20271300</v>
+        <v>20229900</v>
       </c>
       <c r="E8" s="3">
-        <v>19183600</v>
+        <v>18510200</v>
       </c>
       <c r="F8" s="3">
-        <v>15243900</v>
+        <v>15652200</v>
       </c>
       <c r="G8" s="3">
-        <v>11747200</v>
+        <v>12973700</v>
       </c>
       <c r="H8" s="3">
-        <v>13310000</v>
+        <v>13485600</v>
       </c>
       <c r="I8" s="3">
-        <v>12757300</v>
+        <v>13187500</v>
       </c>
       <c r="J8" s="3">
-        <v>12252300</v>
+        <v>13282900</v>
       </c>
       <c r="K8" s="3">
         <v>9909300</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12733000</v>
+        <v>12795400</v>
       </c>
       <c r="E9" s="3">
-        <v>12223500</v>
+        <v>11850000</v>
       </c>
       <c r="F9" s="3">
-        <v>9546400</v>
+        <v>9848700</v>
       </c>
       <c r="G9" s="3">
-        <v>7509500</v>
+        <v>8329100</v>
       </c>
       <c r="H9" s="3">
-        <v>8195100</v>
+        <v>8331300</v>
       </c>
       <c r="I9" s="3">
-        <v>7767600</v>
+        <v>8083400</v>
       </c>
       <c r="J9" s="3">
-        <v>7473000</v>
+        <v>8131600</v>
       </c>
       <c r="K9" s="3">
         <v>6058600</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7538300</v>
+        <v>7434500</v>
       </c>
       <c r="E10" s="3">
-        <v>6960200</v>
+        <v>6660300</v>
       </c>
       <c r="F10" s="3">
-        <v>5697500</v>
+        <v>5803500</v>
       </c>
       <c r="G10" s="3">
-        <v>4237700</v>
+        <v>4644600</v>
       </c>
       <c r="H10" s="3">
-        <v>5114900</v>
+        <v>5154300</v>
       </c>
       <c r="I10" s="3">
-        <v>4989700</v>
+        <v>5104200</v>
       </c>
       <c r="J10" s="3">
-        <v>4779300</v>
+        <v>5151300</v>
       </c>
       <c r="K10" s="3">
         <v>3850700</v>
@@ -875,17 +875,17 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>66100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>49200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>45600</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>36600</v>
+        <v>15500</v>
       </c>
       <c r="E14" s="3">
-        <v>66500</v>
+        <v>63100</v>
       </c>
       <c r="F14" s="3">
-        <v>64200</v>
+        <v>229700</v>
       </c>
       <c r="G14" s="3">
-        <v>100800</v>
-      </c>
-      <c r="H14" s="3">
-        <v>27700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>52100</v>
-      </c>
-      <c r="J14" s="3">
-        <v>27700</v>
+        <v>463600</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>115200</v>
+        <v>583600</v>
       </c>
       <c r="E15" s="3">
-        <v>103000</v>
+        <v>569600</v>
       </c>
       <c r="F15" s="3">
-        <v>93000</v>
+        <v>821100</v>
       </c>
       <c r="G15" s="3">
-        <v>68700</v>
+        <v>741300</v>
       </c>
       <c r="H15" s="3">
-        <v>48700</v>
+        <v>673300</v>
       </c>
       <c r="I15" s="3">
-        <v>47600</v>
+        <v>561000</v>
       </c>
       <c r="J15" s="3">
-        <v>42100</v>
+        <v>548800</v>
       </c>
       <c r="K15" s="3">
         <v>35800</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17680600</v>
+        <v>17629000</v>
       </c>
       <c r="E17" s="3">
-        <v>16873200</v>
+        <v>16217800</v>
       </c>
       <c r="F17" s="3">
-        <v>13564800</v>
+        <v>13698400</v>
       </c>
       <c r="G17" s="3">
-        <v>10846700</v>
+        <v>11518000</v>
       </c>
       <c r="H17" s="3">
-        <v>11595500</v>
+        <v>11749500</v>
       </c>
       <c r="I17" s="3">
-        <v>11317500</v>
+        <v>11700300</v>
       </c>
       <c r="J17" s="3">
-        <v>10856700</v>
+        <v>11773500</v>
       </c>
       <c r="K17" s="3">
         <v>8986000</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2590700</v>
+        <v>2600900</v>
       </c>
       <c r="E18" s="3">
-        <v>2310500</v>
+        <v>2292400</v>
       </c>
       <c r="F18" s="3">
-        <v>1679100</v>
+        <v>1953800</v>
       </c>
       <c r="G18" s="3">
-        <v>900500</v>
+        <v>1455700</v>
       </c>
       <c r="H18" s="3">
-        <v>1714600</v>
+        <v>1736100</v>
       </c>
       <c r="I18" s="3">
-        <v>1439900</v>
+        <v>1487300</v>
       </c>
       <c r="J18" s="3">
-        <v>1395600</v>
+        <v>1509400</v>
       </c>
       <c r="K18" s="3">
         <v>923300</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>47600</v>
+        <v>24300</v>
       </c>
       <c r="E20" s="3">
-        <v>52100</v>
+        <v>21400</v>
       </c>
       <c r="F20" s="3">
-        <v>32100</v>
+        <v>15900</v>
       </c>
       <c r="G20" s="3">
-        <v>19900</v>
+        <v>15900</v>
       </c>
       <c r="H20" s="3">
-        <v>47600</v>
+        <v>5600</v>
       </c>
       <c r="I20" s="3">
-        <v>43200</v>
+        <v>8000</v>
       </c>
       <c r="J20" s="3">
-        <v>44300</v>
+        <v>6000</v>
       </c>
       <c r="K20" s="3">
         <v>14100</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3515400</v>
+        <v>3160200</v>
       </c>
       <c r="E21" s="3">
-        <v>3266100</v>
+        <v>2840700</v>
       </c>
       <c r="F21" s="3">
-        <v>2577200</v>
+        <v>2759000</v>
       </c>
       <c r="G21" s="3">
-        <v>1725500</v>
+        <v>2181000</v>
       </c>
       <c r="H21" s="3">
-        <v>2469800</v>
+        <v>2403800</v>
       </c>
       <c r="I21" s="3">
-        <v>2050100</v>
+        <v>2040300</v>
       </c>
       <c r="J21" s="3">
-        <v>1982500</v>
+        <v>2052100</v>
       </c>
       <c r="K21" s="3">
         <v>1340900</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>198300</v>
+        <v>197900</v>
       </c>
       <c r="E22" s="3">
-        <v>194900</v>
+        <v>188100</v>
       </c>
       <c r="F22" s="3">
-        <v>180500</v>
+        <v>185400</v>
       </c>
       <c r="G22" s="3">
-        <v>150600</v>
+        <v>166400</v>
       </c>
       <c r="H22" s="3">
-        <v>151700</v>
+        <v>153700</v>
       </c>
       <c r="I22" s="3">
-        <v>148400</v>
+        <v>153400</v>
       </c>
       <c r="J22" s="3">
-        <v>156200</v>
+        <v>169300</v>
       </c>
       <c r="K22" s="3">
         <v>157300</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2440000</v>
+        <v>2435100</v>
       </c>
       <c r="E23" s="3">
-        <v>2167600</v>
+        <v>2091500</v>
       </c>
       <c r="F23" s="3">
-        <v>1530700</v>
+        <v>1571700</v>
       </c>
       <c r="G23" s="3">
-        <v>769800</v>
+        <v>850200</v>
       </c>
       <c r="H23" s="3">
-        <v>1610500</v>
+        <v>1631700</v>
       </c>
       <c r="I23" s="3">
-        <v>1334700</v>
+        <v>1379700</v>
       </c>
       <c r="J23" s="3">
-        <v>1283700</v>
+        <v>1391700</v>
       </c>
       <c r="K23" s="3">
         <v>780100</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>591500</v>
+        <v>590300</v>
       </c>
       <c r="E24" s="3">
-        <v>482900</v>
+        <v>466000</v>
       </c>
       <c r="F24" s="3">
-        <v>436400</v>
+        <v>448100</v>
       </c>
       <c r="G24" s="3">
-        <v>218200</v>
+        <v>241000</v>
       </c>
       <c r="H24" s="3">
-        <v>403200</v>
+        <v>408500</v>
       </c>
       <c r="I24" s="3">
-        <v>357800</v>
+        <v>338900</v>
       </c>
       <c r="J24" s="3">
-        <v>167200</v>
+        <v>565600</v>
       </c>
       <c r="K24" s="3">
         <v>184500</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1848600</v>
+        <v>1844800</v>
       </c>
       <c r="E26" s="3">
-        <v>1684700</v>
+        <v>1625500</v>
       </c>
       <c r="F26" s="3">
-        <v>1094300</v>
+        <v>1123600</v>
       </c>
       <c r="G26" s="3">
-        <v>551600</v>
+        <v>609200</v>
       </c>
       <c r="H26" s="3">
-        <v>1207300</v>
+        <v>1223200</v>
       </c>
       <c r="I26" s="3">
-        <v>976900</v>
+        <v>1040800</v>
       </c>
       <c r="J26" s="3">
-        <v>1116500</v>
+        <v>826100</v>
       </c>
       <c r="K26" s="3">
         <v>595700</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1848600</v>
+        <v>1844800</v>
       </c>
       <c r="E27" s="3">
-        <v>1670300</v>
+        <v>1611600</v>
       </c>
       <c r="F27" s="3">
-        <v>1087700</v>
+        <v>1116800</v>
       </c>
       <c r="G27" s="3">
-        <v>551600</v>
+        <v>609200</v>
       </c>
       <c r="H27" s="3">
-        <v>1207300</v>
+        <v>1223200</v>
       </c>
       <c r="I27" s="3">
-        <v>976900</v>
+        <v>1040800</v>
       </c>
       <c r="J27" s="3">
-        <v>1116500</v>
+        <v>826100</v>
       </c>
       <c r="K27" s="3">
         <v>595700</v>
@@ -1529,26 +1529,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>29900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-354400</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-47600</v>
+        <v>-24300</v>
       </c>
       <c r="E32" s="3">
-        <v>-52100</v>
+        <v>-21400</v>
       </c>
       <c r="F32" s="3">
-        <v>-32100</v>
+        <v>-15900</v>
       </c>
       <c r="G32" s="3">
-        <v>-19900</v>
+        <v>-15900</v>
       </c>
       <c r="H32" s="3">
-        <v>-47600</v>
+        <v>-5600</v>
       </c>
       <c r="I32" s="3">
-        <v>-43200</v>
+        <v>-8000</v>
       </c>
       <c r="J32" s="3">
-        <v>-44300</v>
+        <v>-6000</v>
       </c>
       <c r="K32" s="3">
         <v>-14100</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1848600</v>
+        <v>1844800</v>
       </c>
       <c r="E33" s="3">
-        <v>1670300</v>
+        <v>1611600</v>
       </c>
       <c r="F33" s="3">
-        <v>1087700</v>
+        <v>1116800</v>
       </c>
       <c r="G33" s="3">
-        <v>551600</v>
+        <v>609200</v>
       </c>
       <c r="H33" s="3">
-        <v>1207300</v>
+        <v>1223200</v>
       </c>
       <c r="I33" s="3">
-        <v>1006800</v>
+        <v>1040800</v>
       </c>
       <c r="J33" s="3">
-        <v>762000</v>
+        <v>826100</v>
       </c>
       <c r="K33" s="3">
         <v>595700</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1848600</v>
+        <v>1844800</v>
       </c>
       <c r="E35" s="3">
-        <v>1670300</v>
+        <v>1611600</v>
       </c>
       <c r="F35" s="3">
-        <v>1087700</v>
+        <v>1116800</v>
       </c>
       <c r="G35" s="3">
-        <v>551600</v>
+        <v>609200</v>
       </c>
       <c r="H35" s="3">
-        <v>1207300</v>
+        <v>1223200</v>
       </c>
       <c r="I35" s="3">
-        <v>1006800</v>
+        <v>1040800</v>
       </c>
       <c r="J35" s="3">
-        <v>762000</v>
+        <v>826100</v>
       </c>
       <c r="K35" s="3">
         <v>595700</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>515000</v>
+        <v>1568500</v>
       </c>
       <c r="E41" s="3">
-        <v>543800</v>
+        <v>1482300</v>
       </c>
       <c r="F41" s="3">
-        <v>784200</v>
+        <v>1600100</v>
       </c>
       <c r="G41" s="3">
-        <v>712200</v>
+        <v>1863000</v>
       </c>
       <c r="H41" s="3">
-        <v>188300</v>
+        <v>354600</v>
       </c>
       <c r="I41" s="3">
-        <v>309000</v>
+        <v>353800</v>
       </c>
       <c r="J41" s="3">
-        <v>336700</v>
+        <v>432300</v>
       </c>
       <c r="K41" s="3">
         <v>302700</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1685800</v>
+        <v>679800</v>
       </c>
       <c r="E42" s="3">
-        <v>1276000</v>
+        <v>377300</v>
       </c>
       <c r="F42" s="3">
-        <v>838500</v>
+        <v>72800</v>
       </c>
       <c r="G42" s="3">
-        <v>974700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>161700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>33200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>116100</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3021500</v>
+        <v>3259600</v>
       </c>
       <c r="E43" s="3">
-        <v>2979400</v>
+        <v>3194400</v>
       </c>
       <c r="F43" s="3">
-        <v>2762400</v>
+        <v>3029700</v>
       </c>
       <c r="G43" s="3">
-        <v>1781000</v>
+        <v>2141900</v>
       </c>
       <c r="H43" s="3">
-        <v>2180900</v>
+        <v>2209600</v>
       </c>
       <c r="I43" s="3">
-        <v>2119900</v>
+        <v>2191400</v>
       </c>
       <c r="J43" s="3">
-        <v>2468800</v>
+        <v>2676500</v>
       </c>
       <c r="K43" s="3">
         <v>2462900</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1501900</v>
+        <v>1498800</v>
       </c>
       <c r="E44" s="3">
-        <v>1528500</v>
+        <v>1474800</v>
       </c>
       <c r="F44" s="3">
-        <v>1281500</v>
+        <v>1315800</v>
       </c>
       <c r="G44" s="3">
-        <v>754300</v>
+        <v>833000</v>
       </c>
       <c r="H44" s="3">
-        <v>800800</v>
+        <v>811400</v>
       </c>
       <c r="I44" s="3">
-        <v>767600</v>
+        <v>793500</v>
       </c>
       <c r="J44" s="3">
-        <v>719900</v>
+        <v>780500</v>
       </c>
       <c r="K44" s="3">
         <v>730200</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>591500</v>
+        <v>150300</v>
       </c>
       <c r="E45" s="3">
-        <v>919300</v>
+        <v>271500</v>
       </c>
       <c r="F45" s="3">
-        <v>713300</v>
+        <v>417400</v>
       </c>
       <c r="G45" s="3">
-        <v>292400</v>
+        <v>73400</v>
       </c>
       <c r="H45" s="3">
-        <v>105200</v>
+        <v>33700</v>
       </c>
       <c r="I45" s="3">
-        <v>83100</v>
+        <v>32100</v>
       </c>
       <c r="J45" s="3">
-        <v>83100</v>
+        <v>36000</v>
       </c>
       <c r="K45" s="3">
         <v>104200</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7315700</v>
+        <v>7300800</v>
       </c>
       <c r="E46" s="3">
-        <v>7247000</v>
+        <v>6992600</v>
       </c>
       <c r="F46" s="3">
-        <v>6379800</v>
+        <v>6550700</v>
       </c>
       <c r="G46" s="3">
-        <v>4514600</v>
+        <v>4985900</v>
       </c>
       <c r="H46" s="3">
-        <v>3436900</v>
+        <v>3482200</v>
       </c>
       <c r="I46" s="3">
-        <v>3312800</v>
+        <v>3424500</v>
       </c>
       <c r="J46" s="3">
-        <v>3670600</v>
+        <v>3979300</v>
       </c>
       <c r="K46" s="3">
         <v>3716100</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>111600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>205200</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>213800</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>31800</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5919000</v>
+        <v>5906900</v>
       </c>
       <c r="E48" s="3">
-        <v>5760600</v>
+        <v>5558400</v>
       </c>
       <c r="F48" s="3">
-        <v>5812700</v>
+        <v>5968400</v>
       </c>
       <c r="G48" s="3">
-        <v>4275300</v>
+        <v>4721700</v>
       </c>
       <c r="H48" s="3">
-        <v>4657500</v>
+        <v>4718900</v>
       </c>
       <c r="I48" s="3">
-        <v>4306300</v>
+        <v>4451600</v>
       </c>
       <c r="J48" s="3">
-        <v>4249900</v>
+        <v>4607300</v>
       </c>
       <c r="K48" s="3">
         <v>4332400</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18728400</v>
+        <v>18690200</v>
       </c>
       <c r="E49" s="3">
-        <v>18945500</v>
+        <v>18280400</v>
       </c>
       <c r="F49" s="3">
-        <v>19119400</v>
+        <v>19631500</v>
       </c>
       <c r="G49" s="3">
-        <v>12107200</v>
+        <v>13371300</v>
       </c>
       <c r="H49" s="3">
-        <v>12212400</v>
+        <v>12373500</v>
       </c>
       <c r="I49" s="3">
-        <v>12075100</v>
+        <v>12482300</v>
       </c>
       <c r="J49" s="3">
-        <v>12077300</v>
+        <v>13093200</v>
       </c>
       <c r="K49" s="3">
         <v>11686500</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>438600</v>
+        <v>325000</v>
       </c>
       <c r="E52" s="3">
-        <v>513900</v>
+        <v>268200</v>
       </c>
       <c r="F52" s="3">
-        <v>908200</v>
+        <v>650500</v>
       </c>
       <c r="G52" s="3">
-        <v>409800</v>
+        <v>387800</v>
       </c>
       <c r="H52" s="3">
-        <v>388800</v>
+        <v>363600</v>
       </c>
       <c r="I52" s="3">
-        <v>481800</v>
+        <v>455700</v>
       </c>
       <c r="J52" s="3">
-        <v>154000</v>
+        <v>99700</v>
       </c>
       <c r="K52" s="3">
         <v>411200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32401700</v>
+        <v>32335600</v>
       </c>
       <c r="E54" s="3">
-        <v>32467100</v>
+        <v>31327300</v>
       </c>
       <c r="F54" s="3">
-        <v>32220100</v>
+        <v>33083100</v>
       </c>
       <c r="G54" s="3">
-        <v>21306900</v>
+        <v>23531500</v>
       </c>
       <c r="H54" s="3">
-        <v>20695500</v>
+        <v>20968500</v>
       </c>
       <c r="I54" s="3">
-        <v>20176000</v>
+        <v>20856400</v>
       </c>
       <c r="J54" s="3">
-        <v>20151700</v>
+        <v>21846800</v>
       </c>
       <c r="K54" s="3">
         <v>20146300</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2554100</v>
+        <v>2847400</v>
       </c>
       <c r="E57" s="3">
-        <v>2426800</v>
+        <v>2892000</v>
       </c>
       <c r="F57" s="3">
-        <v>1873000</v>
+        <v>2161900</v>
       </c>
       <c r="G57" s="3">
-        <v>1244900</v>
+        <v>1596300</v>
       </c>
       <c r="H57" s="3">
-        <v>1260400</v>
+        <v>1556500</v>
       </c>
       <c r="I57" s="3">
-        <v>1223900</v>
+        <v>1483900</v>
       </c>
       <c r="J57" s="3">
-        <v>1170700</v>
+        <v>1482900</v>
       </c>
       <c r="K57" s="3">
         <v>980800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1439900</v>
+        <v>1436900</v>
       </c>
       <c r="E58" s="3">
-        <v>1479800</v>
+        <v>1427800</v>
       </c>
       <c r="F58" s="3">
-        <v>1495300</v>
+        <v>1535300</v>
       </c>
       <c r="G58" s="3">
-        <v>891600</v>
+        <v>1026300</v>
       </c>
       <c r="H58" s="3">
-        <v>885000</v>
+        <v>896600</v>
       </c>
       <c r="I58" s="3">
-        <v>543800</v>
+        <v>562200</v>
       </c>
       <c r="J58" s="3">
-        <v>303500</v>
+        <v>329000</v>
       </c>
       <c r="K58" s="3">
         <v>949400</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4067100</v>
+        <v>888700</v>
       </c>
       <c r="E59" s="3">
-        <v>4193400</v>
+        <v>769500</v>
       </c>
       <c r="F59" s="3">
-        <v>3380400</v>
+        <v>625500</v>
       </c>
       <c r="G59" s="3">
-        <v>2448900</v>
+        <v>732700</v>
       </c>
       <c r="H59" s="3">
-        <v>2412400</v>
+        <v>604900</v>
       </c>
       <c r="I59" s="3">
-        <v>2432300</v>
+        <v>624000</v>
       </c>
       <c r="J59" s="3">
-        <v>2166500</v>
+        <v>656800</v>
       </c>
       <c r="K59" s="3">
         <v>2140700</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8061100</v>
+        <v>8044700</v>
       </c>
       <c r="E60" s="3">
-        <v>8099900</v>
+        <v>7815500</v>
       </c>
       <c r="F60" s="3">
-        <v>6748600</v>
+        <v>6929400</v>
       </c>
       <c r="G60" s="3">
-        <v>4585500</v>
+        <v>5064200</v>
       </c>
       <c r="H60" s="3">
-        <v>4557800</v>
+        <v>4617900</v>
       </c>
       <c r="I60" s="3">
-        <v>4200000</v>
+        <v>4341700</v>
       </c>
       <c r="J60" s="3">
-        <v>3640700</v>
+        <v>3946900</v>
       </c>
       <c r="K60" s="3">
         <v>4070900</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11182300</v>
+        <v>11310900</v>
       </c>
       <c r="E61" s="3">
-        <v>11708400</v>
+        <v>11480200</v>
       </c>
       <c r="F61" s="3">
-        <v>13058600</v>
+        <v>13458400</v>
       </c>
       <c r="G61" s="3">
-        <v>7068700</v>
+        <v>7806700</v>
       </c>
       <c r="H61" s="3">
-        <v>6226900</v>
+        <v>6309100</v>
       </c>
       <c r="I61" s="3">
-        <v>5678700</v>
+        <v>5870200</v>
       </c>
       <c r="J61" s="3">
-        <v>6063000</v>
+        <v>6573000</v>
       </c>
       <c r="K61" s="3">
         <v>6034800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4324100</v>
+        <v>218900</v>
       </c>
       <c r="E62" s="3">
-        <v>4410500</v>
+        <v>203100</v>
       </c>
       <c r="F62" s="3">
-        <v>4427100</v>
+        <v>225200</v>
       </c>
       <c r="G62" s="3">
-        <v>2979400</v>
+        <v>333900</v>
       </c>
       <c r="H62" s="3">
-        <v>3092400</v>
+        <v>413000</v>
       </c>
       <c r="I62" s="3">
-        <v>3027100</v>
+        <v>496900</v>
       </c>
       <c r="J62" s="3">
-        <v>3043700</v>
+        <v>419100</v>
       </c>
       <c r="K62" s="3">
         <v>3030400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23567500</v>
+        <v>23519400</v>
       </c>
       <c r="E66" s="3">
-        <v>24218800</v>
+        <v>23368600</v>
       </c>
       <c r="F66" s="3">
-        <v>24430300</v>
+        <v>24883400</v>
       </c>
       <c r="G66" s="3">
-        <v>14633600</v>
+        <v>16161500</v>
       </c>
       <c r="H66" s="3">
-        <v>13877100</v>
+        <v>14060200</v>
       </c>
       <c r="I66" s="3">
-        <v>12905800</v>
+        <v>13341000</v>
       </c>
       <c r="J66" s="3">
-        <v>12747400</v>
+        <v>13819600</v>
       </c>
       <c r="K66" s="3">
         <v>13136100</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>9349300</v>
+        <v>9098000</v>
       </c>
       <c r="E72" s="3">
-        <v>8456500</v>
+        <v>7938400</v>
       </c>
       <c r="F72" s="3">
-        <v>7718900</v>
+        <v>7593500</v>
       </c>
       <c r="G72" s="3">
-        <v>7049900</v>
+        <v>7434900</v>
       </c>
       <c r="H72" s="3">
-        <v>7113000</v>
+        <v>6884700</v>
       </c>
       <c r="I72" s="3">
-        <v>7707800</v>
+        <v>7639100</v>
       </c>
       <c r="J72" s="3">
-        <v>7815200</v>
+        <v>8128000</v>
       </c>
       <c r="K72" s="3">
         <v>7335700</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8834200</v>
+        <v>8816200</v>
       </c>
       <c r="E76" s="3">
-        <v>8248300</v>
+        <v>7958700</v>
       </c>
       <c r="F76" s="3">
-        <v>7789800</v>
+        <v>7998400</v>
       </c>
       <c r="G76" s="3">
-        <v>6673300</v>
+        <v>7370000</v>
       </c>
       <c r="H76" s="3">
-        <v>6818400</v>
+        <v>6908300</v>
       </c>
       <c r="I76" s="3">
-        <v>7270300</v>
+        <v>7515500</v>
       </c>
       <c r="J76" s="3">
-        <v>7404300</v>
+        <v>8027100</v>
       </c>
       <c r="K76" s="3">
         <v>7010200</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1848600</v>
+        <v>1844800</v>
       </c>
       <c r="E81" s="3">
-        <v>1670300</v>
+        <v>1611600</v>
       </c>
       <c r="F81" s="3">
-        <v>1087700</v>
+        <v>1116800</v>
       </c>
       <c r="G81" s="3">
-        <v>551600</v>
+        <v>609200</v>
       </c>
       <c r="H81" s="3">
-        <v>1207300</v>
+        <v>1223200</v>
       </c>
       <c r="I81" s="3">
-        <v>1006800</v>
+        <v>1040800</v>
       </c>
       <c r="J81" s="3">
-        <v>762000</v>
+        <v>826100</v>
       </c>
       <c r="K81" s="3">
         <v>595700</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>877200</v>
+        <v>709600</v>
       </c>
       <c r="E83" s="3">
-        <v>903800</v>
+        <v>717100</v>
       </c>
       <c r="F83" s="3">
-        <v>866100</v>
+        <v>719900</v>
       </c>
       <c r="G83" s="3">
-        <v>805200</v>
+        <v>665400</v>
       </c>
       <c r="H83" s="3">
-        <v>707800</v>
+        <v>615000</v>
       </c>
       <c r="I83" s="3">
-        <v>567100</v>
+        <v>502600</v>
       </c>
       <c r="J83" s="3">
-        <v>542700</v>
+        <v>492300</v>
       </c>
       <c r="K83" s="3">
         <v>403600</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3107900</v>
+        <v>3101600</v>
       </c>
       <c r="E89" s="3">
-        <v>3247500</v>
+        <v>3133500</v>
       </c>
       <c r="F89" s="3">
-        <v>2344800</v>
+        <v>2407600</v>
       </c>
       <c r="G89" s="3">
-        <v>1650300</v>
+        <v>1822600</v>
       </c>
       <c r="H89" s="3">
-        <v>2108900</v>
+        <v>2136700</v>
       </c>
       <c r="I89" s="3">
-        <v>2000300</v>
+        <v>2067800</v>
       </c>
       <c r="J89" s="3">
-        <v>1797600</v>
+        <v>1948800</v>
       </c>
       <c r="K89" s="3">
         <v>1349700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-744300</v>
+        <v>-742800</v>
       </c>
       <c r="E91" s="3">
-        <v>-553800</v>
+        <v>-534400</v>
       </c>
       <c r="F91" s="3">
-        <v>-386600</v>
+        <v>-396900</v>
       </c>
       <c r="G91" s="3">
-        <v>-385400</v>
+        <v>-425700</v>
       </c>
       <c r="H91" s="3">
-        <v>-560400</v>
+        <v>-567800</v>
       </c>
       <c r="I91" s="3">
-        <v>-581500</v>
+        <v>-601100</v>
       </c>
       <c r="J91" s="3">
-        <v>-536100</v>
+        <v>-581200</v>
       </c>
       <c r="K91" s="3">
         <v>-498000</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1037800</v>
+        <v>-1035700</v>
       </c>
       <c r="E94" s="3">
-        <v>-714400</v>
+        <v>-689300</v>
       </c>
       <c r="F94" s="3">
-        <v>-6208100</v>
+        <v>-6374400</v>
       </c>
       <c r="G94" s="3">
-        <v>-409800</v>
+        <v>-452600</v>
       </c>
       <c r="H94" s="3">
-        <v>-663500</v>
+        <v>-672200</v>
       </c>
       <c r="I94" s="3">
-        <v>-660100</v>
+        <v>-682400</v>
       </c>
       <c r="J94" s="3">
-        <v>-540500</v>
+        <v>-586000</v>
       </c>
       <c r="K94" s="3">
         <v>-415600</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-931500</v>
+        <v>929600</v>
       </c>
       <c r="E96" s="3">
-        <v>-845100</v>
+        <v>815400</v>
       </c>
       <c r="F96" s="3">
-        <v>-706600</v>
+        <v>725600</v>
       </c>
       <c r="G96" s="3">
-        <v>-427500</v>
+        <v>472200</v>
       </c>
       <c r="H96" s="3">
-        <v>-635800</v>
+        <v>644100</v>
       </c>
       <c r="I96" s="3">
-        <v>-568200</v>
+        <v>587400</v>
       </c>
       <c r="J96" s="3">
-        <v>-541600</v>
+        <v>587200</v>
       </c>
       <c r="K96" s="3">
         <v>-221300</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2018000</v>
+        <v>-2013900</v>
       </c>
       <c r="E100" s="3">
-        <v>-2520900</v>
+        <v>-2432400</v>
       </c>
       <c r="F100" s="3">
-        <v>3642900</v>
+        <v>3740500</v>
       </c>
       <c r="G100" s="3">
-        <v>110800</v>
+        <v>122300</v>
       </c>
       <c r="H100" s="3">
-        <v>-1442100</v>
+        <v>-1461100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1394500</v>
+        <v>-1441500</v>
       </c>
       <c r="J100" s="3">
-        <v>-1276000</v>
+        <v>-1383300</v>
       </c>
       <c r="K100" s="3">
         <v>-679200</v>
@@ -4207,22 +4207,22 @@
         <v>-16600</v>
       </c>
       <c r="E101" s="3">
-        <v>-34300</v>
+        <v>-33100</v>
       </c>
       <c r="F101" s="3">
-        <v>91900</v>
+        <v>94400</v>
       </c>
       <c r="G101" s="3">
-        <v>-14400</v>
+        <v>-15900</v>
       </c>
       <c r="H101" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="I101" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="J101" s="3">
-        <v>-10000</v>
+        <v>-10800</v>
       </c>
       <c r="K101" s="3">
         <v>-5400</v>
@@ -4249,22 +4249,22 @@
         <v>35400</v>
       </c>
       <c r="E102" s="3">
-        <v>-22200</v>
+        <v>-21400</v>
       </c>
       <c r="F102" s="3">
-        <v>-128500</v>
+        <v>-131900</v>
       </c>
       <c r="G102" s="3">
-        <v>1336900</v>
+        <v>1476500</v>
       </c>
       <c r="H102" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="I102" s="3">
-        <v>-56500</v>
+        <v>-58400</v>
       </c>
       <c r="J102" s="3">
-        <v>-28800</v>
+        <v>-31200</v>
       </c>
       <c r="K102" s="3">
         <v>249600</v>

--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21159500</v>
+      </c>
+      <c r="E8" s="3">
         <v>20229900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18510200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15652200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12973700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13485600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13187500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13282900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9909300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6460600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7019600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9823200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8852100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13619400</v>
+      </c>
+      <c r="E9" s="3">
         <v>12795400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11850000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9848700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8329100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8331300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8083400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8131600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6058600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12734500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14979800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6399700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5667900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7540100</v>
+      </c>
+      <c r="E10" s="3">
         <v>7434500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6660300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5803500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4644600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5154300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5104200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5151300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3850700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-6273800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-7960200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3423500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3184200</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,20 +888,20 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>66100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>49400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>49200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>45600</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,26 +960,29 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>214300</v>
+      </c>
+      <c r="E14" s="3">
         <v>15500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>63100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>229700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>463600</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -974,63 +993,69 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>66400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>91500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>143500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>93300</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>965900</v>
+      </c>
+      <c r="E15" s="3">
         <v>583600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>569600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>821100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>741300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>673300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>561000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>548800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>191900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>238200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>227300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>235000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18738000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17629000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16217800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13698400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11518000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11749500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11700300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11773500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8986000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5685900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6176200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8729900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7833100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2421600</v>
+      </c>
+      <c r="E18" s="3">
         <v>2600900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2292400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1953800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1455700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1736100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1487300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1509400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>923300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>774800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>843400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1093300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1018900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E20" s="3">
         <v>24300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>21400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>15900</v>
       </c>
       <c r="G20" s="3">
         <v>15900</v>
       </c>
       <c r="H20" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I20" s="3">
         <v>5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>32700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-130400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3378200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3160200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2840700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2759000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2181000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2403800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2040300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2052100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1340900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1034300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1139900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1329900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1390600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>281600</v>
+      </c>
+      <c r="E22" s="3">
         <v>197900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>188100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>185400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>166400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>153700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>153400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>169300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>157300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>129600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>133200</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>103200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2004300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2435100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2091500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1571700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>850200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1631700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1379700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1391700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>780100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>657400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>742900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>962900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>919000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>509400</v>
+      </c>
+      <c r="E24" s="3">
         <v>590300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>466000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>448100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>241000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>408500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>338900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>565600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>184500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>133700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>196500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>165100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>175700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1495000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1844800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1625500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1123600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>609200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1223200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1040800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>826100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>595700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>523700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>546500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>797900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>743300</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1468100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1844800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1611600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1116800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>609200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1223200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1040800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>826100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>595700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>523700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>546500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>797900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>743300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1610,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-24300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-21400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-15900</v>
       </c>
       <c r="G32" s="3">
         <v>-15900</v>
       </c>
       <c r="H32" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-32700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>130400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1468100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1844800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1611600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1116800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>609200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1223200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1040800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>826100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>595700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>523700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>546500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>797900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>743300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1468100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1844800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1611600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1116800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>609200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1223200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1040800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>826100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>595700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>523700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>546500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>797900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>743300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,65 +1986,69 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1618200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1568500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1482300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1600100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1863000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>354600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>353800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>432300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>302700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>412400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>631200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>410300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>791700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E42" s="3">
         <v>679800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>377300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>72800</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1970,208 +2059,223 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>116100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>79600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36100</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2806700</v>
+      </c>
+      <c r="E43" s="3">
         <v>3259600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3194400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3029700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2141900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2209600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2191400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2676500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2462900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3935200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4700400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1918700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1644800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1664800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1498800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1474800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1315800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>833000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>811400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>793500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>780500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>730200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1100400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1282700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>540700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>423800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>627400</v>
+      </c>
+      <c r="E45" s="3">
         <v>150300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>271500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>417400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>73400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>314400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>513700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>202200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>172400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6872300</v>
+      </c>
+      <c r="E46" s="3">
         <v>7300800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6992600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6550700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4985900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3482200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3424500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3979300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3716100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1922200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2267200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3071800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3032700</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>111600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>205200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>213800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>31800</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -2179,8 +2283,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6661100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5906900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5558400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5968400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4721700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4718900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4451600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4607300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4332400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5414300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6150200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2814700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2549600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18051600</v>
+      </c>
+      <c r="E49" s="3">
         <v>18690200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18280400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19631500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13371300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12373500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12482300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13093200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11686500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10163100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11288700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4937900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4452400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>588100</v>
+      </c>
+      <c r="E52" s="3">
         <v>325000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>268200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>650500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>387800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>363600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>455700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>99700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>411200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>372600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>493400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>569400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>407400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32198000</v>
+      </c>
+      <c r="E54" s="3">
         <v>32335600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31327300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33083100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23531500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20968500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20856400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21846800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20146300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7141500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7957900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11393800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10442000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5990300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2847400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2892000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2161900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1596300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1556500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1483900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1482900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>980800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2469300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2853200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>754800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1481200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1440100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1436900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1427800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1535300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1026300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>896600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>562200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>329000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>949400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>890100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1304100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>132800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>693900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>999100</v>
+      </c>
+      <c r="E59" s="3">
         <v>888700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>769500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>625500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>732700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>604900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>624000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>656800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2140700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2534600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1738100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>656600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8436700</v>
+      </c>
+      <c r="E60" s="3">
         <v>8044700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7815500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6929400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5064200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4617900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4341700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3946900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4070900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2047700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2433200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2625700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2831700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10457600</v>
+      </c>
+      <c r="E61" s="3">
         <v>11310900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11480200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13458400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7806700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6309100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5870200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6573000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6034800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3186900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3083600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4457000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3111700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>201900</v>
+      </c>
+      <c r="E62" s="3">
         <v>218900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>203100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>225200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>333900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>413000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>496900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>419100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3030400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2151800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2453500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1583800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1541600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22895700</v>
+      </c>
+      <c r="E66" s="3">
         <v>23519400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23368600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24883400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16161500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14060200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13341000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13819600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13136100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6252400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6617700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8666500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7485100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9112700</v>
+      </c>
+      <c r="E72" s="3">
         <v>9098000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7938400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7593500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7434900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6884700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7639100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8128000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7335700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4037300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3770100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1886400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1236300</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8788700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8816200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7958700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7998400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7370000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6908300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7515500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8027100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7010200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>889100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1340200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2727300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2956900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1468100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1844800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1611600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1116800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>609200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1223200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1040800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>826100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>595700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>523700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>546500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>797900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>743300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>777500</v>
+      </c>
+      <c r="E83" s="3">
         <v>709600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>717100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>719900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>665400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>615000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>502600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>492300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>403600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>252100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>263100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>368400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>367800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3169100</v>
+      </c>
+      <c r="E89" s="3">
         <v>3101600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3133500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2407600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1822600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2136700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2067800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1948800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1349700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>941200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>920200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>996400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1039800</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-818900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-742800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-534400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-396900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-425700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-567800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-601100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-581200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-498000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-625800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-625500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-374400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-415000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2026100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-689300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6374400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-452600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-672200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-682400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-586000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-415600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-277700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-233700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-394700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-409600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>942100</v>
+      </c>
+      <c r="E96" s="3">
         <v>929600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>815400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>725600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>472200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>644100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>587400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>587200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-221300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-499200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-486600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-254800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-205300</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1007400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2013900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2432400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3740500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>122300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1461100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1441500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1383300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-679200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-699200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-764400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1071800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-610500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-16600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-33100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>94400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>17900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>20900</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E102" s="3">
         <v>35400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-131900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1476500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-58400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>249600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-74500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-452200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -774,10 +774,10 @@
         <v>13619400</v>
       </c>
       <c r="E9" s="3">
-        <v>12795400</v>
+        <v>12789900</v>
       </c>
       <c r="F9" s="3">
-        <v>11850000</v>
+        <v>11838200</v>
       </c>
       <c r="G9" s="3">
         <v>9848700</v>
@@ -819,10 +819,10 @@
         <v>7540100</v>
       </c>
       <c r="E10" s="3">
-        <v>7434500</v>
+        <v>7440000</v>
       </c>
       <c r="F10" s="3">
-        <v>6660300</v>
+        <v>6672000</v>
       </c>
       <c r="G10" s="3">
         <v>5803500</v>
@@ -970,13 +970,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>214300</v>
+        <v>462800</v>
       </c>
       <c r="E14" s="3">
-        <v>15500</v>
+        <v>7700</v>
       </c>
       <c r="F14" s="3">
-        <v>63100</v>
+        <v>71600</v>
       </c>
       <c r="G14" s="3">
         <v>229700</v>
@@ -1015,13 +1015,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>965900</v>
+        <v>655300</v>
       </c>
       <c r="E15" s="3">
         <v>583600</v>
       </c>
       <c r="F15" s="3">
-        <v>569600</v>
+        <v>825100</v>
       </c>
       <c r="G15" s="3">
         <v>821100</v>
@@ -1076,13 +1076,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18738000</v>
+        <v>18489500</v>
       </c>
       <c r="E17" s="3">
-        <v>17629000</v>
+        <v>17636800</v>
       </c>
       <c r="F17" s="3">
-        <v>16217800</v>
+        <v>16209300</v>
       </c>
       <c r="G17" s="3">
         <v>13698400</v>
@@ -1121,13 +1121,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2421600</v>
+        <v>2670000</v>
       </c>
       <c r="E18" s="3">
-        <v>2600900</v>
+        <v>2593100</v>
       </c>
       <c r="F18" s="3">
-        <v>2292400</v>
+        <v>2301000</v>
       </c>
       <c r="G18" s="3">
         <v>1953800</v>
@@ -1185,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>9300</v>
+        <v>18600</v>
       </c>
       <c r="E20" s="3">
         <v>24300</v>
@@ -1230,13 +1230,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3378200</v>
+        <v>3306800</v>
       </c>
       <c r="E21" s="3">
-        <v>3160200</v>
+        <v>3152400</v>
       </c>
       <c r="F21" s="3">
-        <v>2840700</v>
+        <v>3104600</v>
       </c>
       <c r="G21" s="3">
         <v>2759000</v>
@@ -1275,7 +1275,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>281600</v>
+        <v>272300</v>
       </c>
       <c r="E22" s="3">
         <v>197900</v>
@@ -1725,7 +1725,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-9300</v>
+        <v>-18600</v>
       </c>
       <c r="E32" s="3">
         <v>-24300</v>
@@ -2083,7 +2083,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2806700</v>
+        <v>3071700</v>
       </c>
       <c r="E43" s="3">
         <v>3259600</v>
@@ -2173,7 +2173,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>627400</v>
+        <v>153200</v>
       </c>
       <c r="E45" s="3">
         <v>150300</v>
@@ -2262,8 +2262,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>138700</v>
       </c>
       <c r="E47" s="3">
         <v>111600</v>
@@ -2488,7 +2488,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>588100</v>
+        <v>449300</v>
       </c>
       <c r="E52" s="3">
         <v>325000</v>
@@ -2661,10 +2661,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5990300</v>
+        <v>3137000</v>
       </c>
       <c r="E57" s="3">
-        <v>2847400</v>
+        <v>2834100</v>
       </c>
       <c r="F57" s="3">
         <v>2892000</v>
@@ -2751,7 +2751,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>999100</v>
+        <v>1018700</v>
       </c>
       <c r="E59" s="3">
         <v>888700</v>
@@ -2841,7 +2841,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10457600</v>
+        <v>10410000</v>
       </c>
       <c r="E61" s="3">
         <v>11310900</v>
@@ -2886,7 +2886,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>201900</v>
+        <v>249500</v>
       </c>
       <c r="E62" s="3">
         <v>218900</v>
@@ -3694,7 +3694,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>777500</v>
+        <v>747500</v>
       </c>
       <c r="E83" s="3">
         <v>709600</v>

--- a/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCEP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>CCEP</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24540300</v>
+      </c>
+      <c r="E8" s="3">
         <v>21159500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20229900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18510200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15652200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12973700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13485600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13187500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13282900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9909300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6460600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7019600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9823200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8852100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15809600</v>
+      </c>
+      <c r="E9" s="3">
         <v>13619400</v>
       </c>
-      <c r="E9" s="3">
-        <v>12789900</v>
-      </c>
       <c r="F9" s="3">
+        <v>12792100</v>
+      </c>
+      <c r="G9" s="3">
         <v>11838200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9848700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8329100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8331300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8083400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8131600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6058600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12734500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14979800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6399700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5667900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8730800</v>
+      </c>
+      <c r="E10" s="3">
         <v>7540100</v>
       </c>
-      <c r="E10" s="3">
-        <v>7440000</v>
-      </c>
       <c r="F10" s="3">
+        <v>7437800</v>
+      </c>
+      <c r="G10" s="3">
         <v>6672000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5803500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4644600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5154300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5104200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5151300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3850700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-6273800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-7960200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3423500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3184200</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,20 +904,20 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>66100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>49400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>49200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>45600</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,29 +979,32 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>462800</v>
+        <v>-5900</v>
       </c>
       <c r="E14" s="3">
-        <v>7700</v>
+        <v>491800</v>
       </c>
       <c r="F14" s="3">
-        <v>71600</v>
+        <v>117200</v>
       </c>
       <c r="G14" s="3">
+        <v>74800</v>
+      </c>
+      <c r="H14" s="3">
         <v>229700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>463600</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -996,66 +1015,72 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>66400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>91500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>143500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>93300</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>747900</v>
+      </c>
+      <c r="E15" s="3">
         <v>655300</v>
       </c>
-      <c r="E15" s="3">
-        <v>583600</v>
-      </c>
       <c r="F15" s="3">
+        <v>863300</v>
+      </c>
+      <c r="G15" s="3">
         <v>825100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>821100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>741300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>673300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>561000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>548800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>191900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>238200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>227300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>235000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18489500</v>
+        <v>21266900</v>
       </c>
       <c r="E17" s="3">
-        <v>17636800</v>
+        <v>18460500</v>
       </c>
       <c r="F17" s="3">
-        <v>16209300</v>
+        <v>17527400</v>
       </c>
       <c r="G17" s="3">
+        <v>16206000</v>
+      </c>
+      <c r="H17" s="3">
         <v>13698400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11518000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11749500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11700300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11773500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8986000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5685900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6176200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8729900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7833100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2670000</v>
+        <v>3273500</v>
       </c>
       <c r="E18" s="3">
-        <v>2593100</v>
+        <v>2699000</v>
       </c>
       <c r="F18" s="3">
-        <v>2301000</v>
+        <v>2702600</v>
       </c>
       <c r="G18" s="3">
+        <v>2304200</v>
+      </c>
+      <c r="H18" s="3">
         <v>1953800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1455700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1736100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1487300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1509400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>923300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>774800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>843400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1093300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1018900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E20" s="3">
         <v>18600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>24300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>21400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>15900</v>
       </c>
       <c r="H20" s="3">
         <v>15900</v>
       </c>
       <c r="I20" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J20" s="3">
         <v>5600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-130400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3306800</v>
+        <v>3986100</v>
       </c>
       <c r="E21" s="3">
-        <v>3152400</v>
+        <v>3335700</v>
       </c>
       <c r="F21" s="3">
-        <v>3104600</v>
+        <v>3541500</v>
       </c>
       <c r="G21" s="3">
+        <v>3107800</v>
+      </c>
+      <c r="H21" s="3">
         <v>2759000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2181000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2403800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2040300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2052100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1340900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1034300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1139900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1329900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1390600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>348700</v>
+      </c>
+      <c r="E22" s="3">
         <v>272300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>197900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>188100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>185400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>166400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>153700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>153400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>169300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>157300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>129600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>133200</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>103200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3016300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2004300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2435100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2091500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1571700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>850200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1631700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1379700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1391700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>780100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>657400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>742900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>962900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>919000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>692700</v>
+      </c>
+      <c r="E24" s="3">
         <v>509400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>590300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>466000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>448100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>241000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>408500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>338900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>565600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>184500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>133700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>196500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>165100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>175700</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2323600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1495000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1844800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1625500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1123600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>609200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1223200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1040800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>826100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>595700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>523700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>546500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>797900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>743300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2280200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1468100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1844800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1611600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1116800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>609200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1223200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1040800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>826100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>595700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>523700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>546500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>797900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>743300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-24300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-21400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-15900</v>
       </c>
       <c r="H32" s="3">
         <v>-15900</v>
       </c>
       <c r="I32" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-5600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>130400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2280100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1468100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1844800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1611600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1116800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>609200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1223200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1040800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>826100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>595700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>523700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>546500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>797900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>743300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2280100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1468100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1844800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1611600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1116800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>609200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1223200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1040800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>826100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>595700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>523700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>546500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>797900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>743300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,71 +2072,75 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1077800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1618200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1568500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1482300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1600100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1863000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>354600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>353800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>432300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>302700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>412400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>631200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>410300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>791700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E42" s="3">
         <v>155300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>679800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>377300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>72800</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2062,223 +2151,238 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>116100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>79600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>36100</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3878100</v>
+      </c>
+      <c r="E43" s="3">
         <v>3071700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3259600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3194400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3029700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2141900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2209600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2191400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2676500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2462900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3935200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4700400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1918700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1644800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1816400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1664800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1498800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1474800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1315800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>833000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>811400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>793500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>780500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>730200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1100400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1282700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>540700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>423800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E45" s="3">
         <v>153200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>150300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>271500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>417400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>73400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>104200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>314400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>513700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>202200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>172400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7137500</v>
+      </c>
+      <c r="E46" s="3">
         <v>6872300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7300800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6992600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6550700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4985900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3482200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3424500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3979300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3716100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1922200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2267200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3071800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3032700</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E47" s="3">
         <v>138700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>111600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>205200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>213800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>31800</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -2286,8 +2390,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2301,99 +2405,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7226700</v>
+      </c>
+      <c r="E48" s="3">
         <v>6661100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5906900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5558400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5968400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4721700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4718900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4451600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4607300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4332400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5414300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6150200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2814700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2549600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19990600</v>
+      </c>
+      <c r="E49" s="3">
         <v>18051600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18690200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18280400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19631500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13371300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12373500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12482300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13093200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11686500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10163100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11288700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4937900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4452400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>618800</v>
+      </c>
+      <c r="E52" s="3">
         <v>449300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>325000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>268200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>650500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>387800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>363600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>455700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>99700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>411200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>372600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>493400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>569400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>407400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35073400</v>
+      </c>
+      <c r="E54" s="3">
         <v>32198000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32335600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31327300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33083100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23531500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20968500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20856400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21846800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20146300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7141500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7957900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11393800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10442000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3551700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3137000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2834100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2892000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2161900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1596300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1556500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1483900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1482900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>980800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2469300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2853200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>754800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1481200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>551800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1440100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1436900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1427800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1535300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1026300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>896600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>562200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>329000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>949400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>890100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1304100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>132800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>693900</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1153000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1018700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>888700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>769500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>625500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>732700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>604900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>624000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>656800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2140700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2534600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2900700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1738100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>656600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8905700</v>
+      </c>
+      <c r="E60" s="3">
         <v>8436700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8044700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7815500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6929400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5064200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4617900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4341700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3946900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4070900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2047700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2433200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2625700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2831700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12121600</v>
+      </c>
+      <c r="E61" s="3">
         <v>10410000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11310900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11480200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13458400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7806700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6309100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5870200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6573000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6034800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3186900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3083600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4457000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3111700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>221900</v>
+      </c>
+      <c r="E62" s="3">
         <v>249500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>218900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>203100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>225200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>333900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>413000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>496900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>419100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3030400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2151800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2453500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1583800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1541600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25324600</v>
+      </c>
+      <c r="E66" s="3">
         <v>22895700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23519400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23368600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24883400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16161500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14060200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13341000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13819600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13136100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6252400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6617700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8666500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7485100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10355800</v>
+      </c>
+      <c r="E72" s="3">
         <v>9112700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9098000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7938400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7593500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7434900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6884700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7639100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8128000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7335700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4037300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3770100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1886400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1236300</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9199200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8788700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8816200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7958700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7998400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7370000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6908300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7515500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8027100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7010200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>889100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1340200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2727300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2956900</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2280100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1468100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1844800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1611600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1116800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>609200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1223200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1040800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>826100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>595700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>523700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>546500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>797900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>743300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>898200</v>
+      </c>
+      <c r="E83" s="3">
         <v>747500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>709600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>717100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>719900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>665400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>615000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>502600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>492300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>403600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>252100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>263100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>368400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>367800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3467200</v>
+      </c>
+      <c r="E89" s="3">
         <v>3169100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3101600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3133500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2407600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1822600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2136700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2067800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1948800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1349700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>941200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>920200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>996400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1039800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-880600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-818900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-742800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-534400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-396900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-425700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-567800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-601100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-581200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-498000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-625800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-625500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-374400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-415000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-742000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2026100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-689300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6374400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-452600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-672200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-682400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-586000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-415600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-277700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-233700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-394700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-409600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1088400</v>
+      </c>
+      <c r="E96" s="3">
         <v>942100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>929600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>815400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>725600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>472200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>644100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>587400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>587200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-221300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-499200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-486600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-254800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-205300</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3393200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1007400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2013900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2432400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3740500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>122300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1461100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1441500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1383300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-679200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-699200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-764400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1071800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-610500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-89200</v>
+      </c>
+      <c r="E101" s="3">
         <v>13500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-16600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-33100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>94400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-15900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>17900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>20900</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-757300</v>
+      </c>
+      <c r="E102" s="3">
         <v>149100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>35400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-131900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1476500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-58400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>249600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-74500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-452200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
